--- a/data/dental_clinic_database.xlsx
+++ b/data/dental_clinic_database.xlsx
@@ -8,9 +8,11 @@
     <sheet name="Appointments" sheetId="3" r:id="rId3"/>
     <sheet name="Payments" sheetId="4" r:id="rId4"/>
     <sheet name="README" sheetId="5" r:id="rId5"/>
-    <sheet name="DailyQueue" sheetId="6" r:id="rId6"/>
-    <sheet name="Treatments" sheetId="7" r:id="rId7"/>
-    <sheet name="Users" sheetId="8" r:id="rId8"/>
+    <sheet name="Users" sheetId="6" r:id="rId6"/>
+    <sheet name="DailyQueue" sheetId="7" r:id="rId7"/>
+    <sheet name="Treatments" sheetId="8" r:id="rId8"/>
+    <sheet name="Common_Treatments" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -404,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,6 +462,9 @@
       <c r="G2" t="b">
         <v>0</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
       <c r="I2" t="str">
         <v>2026-07-01T08:15:20.000Z</v>
       </c>
@@ -521,6 +526,9 @@
       <c r="G4" t="b">
         <v>0</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
       <c r="I4" t="str">
         <v>2026-07-03T10:30:05.000Z</v>
       </c>
@@ -550,6 +558,9 @@
       <c r="G5" t="b">
         <v>0</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
       <c r="I5" t="str">
         <v>2026-07-04T11:45:33.000Z</v>
       </c>
@@ -579,6 +590,9 @@
       <c r="G6" t="b">
         <v>0</v>
       </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
       <c r="I6" t="str">
         <v>2026-07-05T07:20:48.000Z</v>
       </c>
@@ -640,6 +654,9 @@
       <c r="G8" t="b">
         <v>0</v>
       </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
       <c r="I8" t="str">
         <v>2026-07-07T13:25:41.000Z</v>
       </c>
@@ -701,6 +718,9 @@
       <c r="G10" t="b">
         <v>0</v>
       </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
       <c r="I10" t="str">
         <v>2026-07-09T08:35:28.000Z</v>
       </c>
@@ -730,6 +750,9 @@
       <c r="G11" t="b">
         <v>0</v>
       </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
       <c r="I11" t="str">
         <v>2026-07-10T09:50:37.000Z</v>
       </c>
@@ -759,6 +782,9 @@
       <c r="G12" t="b">
         <v>0</v>
       </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
       <c r="I12" t="str">
         <v>2026-07-11T10:05:52.000Z</v>
       </c>
@@ -820,6 +846,9 @@
       <c r="G14" t="b">
         <v>0</v>
       </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
       <c r="I14" t="str">
         <v>2026-07-13T12:32:10.000Z</v>
       </c>
@@ -881,6 +910,9 @@
       <c r="G16" t="b">
         <v>0</v>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
       <c r="I16" t="str">
         <v>2026-07-15T14:55:09.000Z</v>
       </c>
@@ -942,6 +974,9 @@
       <c r="G18" t="b">
         <v>0</v>
       </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
       <c r="I18" t="str">
         <v>2026-07-16T06:18:42.000Z</v>
       </c>
@@ -971,6 +1006,9 @@
       <c r="G19" t="b">
         <v>0</v>
       </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
       <c r="I19" t="str">
         <v>2026-07-16T06:24:15.000Z</v>
       </c>
@@ -1000,6 +1038,9 @@
       <c r="G20" t="b">
         <v>0</v>
       </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
       <c r="I20" t="str">
         <v>2026-07-16T06:31:50.000Z</v>
       </c>
@@ -1061,6 +1102,9 @@
       <c r="G22" t="b">
         <v>0</v>
       </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
       <c r="I22" t="str">
         <v>2026-07-16T06:48:27.000Z</v>
       </c>
@@ -1122,6 +1166,9 @@
       <c r="G24" t="b">
         <v>0</v>
       </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
       <c r="I24" t="str">
         <v>2026-07-16T07:02:46.000Z</v>
       </c>
@@ -1183,17 +1230,95 @@
       <c r="G26" t="b">
         <v>0</v>
       </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
       <c r="I26" t="str">
         <v>2026-07-16T07:20:18.000Z</v>
       </c>
       <c r="J26" t="str">
         <v>2026-07-16T07:20:18.000Z</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PAT_104d77f7</v>
+      </c>
+      <c r="B27" t="str">
+        <v>new</v>
+      </c>
+      <c r="C27" t="str">
+        <v>0771234560</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="str">
+        <v>jjj</v>
+      </c>
+      <c r="I27" t="str">
+        <v>2026-07-27T17:10:16.792Z</v>
+      </c>
+      <c r="J27" t="str">
+        <v>2026-07-27T17:10:16.792Z</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PAT_a087a411</v>
+      </c>
+      <c r="B28" t="str">
+        <v>new1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>0715555000</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="str">
+        <v>ffjgk</v>
+      </c>
+      <c r="I28" t="str">
+        <v>2026-07-28T06:08:54.377Z</v>
+      </c>
+      <c r="J28" t="str">
+        <v>2026-07-28T06:08:54.377Z</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J28"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1227,7 +1352,7 @@
         <v>DEN_0001</v>
       </c>
       <c r="B2" t="str">
-        <v>Dr. Nimal Silva</v>
+        <v>Dr. UHPKJ Bandu</v>
       </c>
       <c r="C2" t="str">
         <v>0715555555</v>
@@ -1238,8 +1363,8 @@
       <c r="E2">
         <v>46199.354166666664</v>
       </c>
-      <c r="F2">
-        <v>46199.354166666664</v>
+      <c r="F2" t="str">
+        <v>2026-07-27T15:49:25.289Z</v>
       </c>
     </row>
   </sheetData>
@@ -1252,7 +1377,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1265,121 +1390,130 @@
         <v>dentist_id</v>
       </c>
       <c r="D1" t="str">
+        <v>appointment_number</v>
+      </c>
+      <c r="E1" t="str">
         <v>appointment_date</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>appointment_time</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>reason_for_visit</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>status</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>created_at</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>updated_at</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>checked_in_time</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>treatment_started_at</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>treatment_completed_at</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>completed_at</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>APP_20260720_0001</v>
+        <v>APP_20260728_0001</v>
       </c>
       <c r="B2" t="str">
-        <v>PAT_3c4d5e6f</v>
+        <v>PAT_1a2b3c4d</v>
       </c>
       <c r="C2" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D2" t="str">
-        <v>2026-07-20</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>08:00</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F2" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="G2" t="str">
         <v>Dental Check-up</v>
       </c>
-      <c r="G2" t="str">
-        <v>Completed</v>
-      </c>
       <c r="H2" t="str">
-        <v>2026-07-20T11:30:09.373Z</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-07-20T11:34:38.364Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-07-20T11:31:06.755Z</v>
+        <v>2026-07-28T12:34:40.757Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-07-20T11:31:13.545Z</v>
+        <v>2026-07-28T12:33:31.509Z</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-07-20T11:31:39.406Z</v>
+        <v>2026-07-28T12:34:22.179Z</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-20T11:34:38.364Z</v>
+        <v>2026-07-28T12:34:40.757Z</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>APP_20260720_0002</v>
+        <v>APP_20260728_0002</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_5e6f7a8b</v>
+        <v>PAT_3c4d5e6f</v>
       </c>
       <c r="C3" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D3" t="str">
-        <v>2026-07-20</v>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>08:30</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F3" t="str">
-        <v>Root Canal Treatment</v>
+        <v>16:15</v>
       </c>
       <c r="G3" t="str">
-        <v>Completed</v>
+        <v>Tooth Pain</v>
       </c>
       <c r="H3" t="str">
-        <v>2026-07-20T11:30:15.942Z</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-07-20T11:34:39.368Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-07-20T11:31:07.094Z</v>
+        <v>2026-07-28T12:36:16.971Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-07-20T11:33:19.184Z</v>
+        <v>2026-07-28T12:33:34.362Z</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-07-20T11:33:34.933Z</v>
+        <v>2026-07-28T12:34:52.401Z</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-07-20T11:34:39.368Z</v>
+        <v>2026-07-28T12:36:16.971Z</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>APP_20260720_0003</v>
+        <v>APP_20260728_0003</v>
       </c>
       <c r="B4" t="str">
         <v>PAT_5e6f7a8b</v>
@@ -1387,334 +1521,446 @@
       <c r="C4" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D4" t="str">
-        <v>2026-07-20</v>
+      <c r="D4">
+        <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>09:00</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F4" t="str">
-        <v>Teeth Cleaning</v>
+        <v>16:30</v>
       </c>
       <c r="G4" t="str">
-        <v>Completed</v>
+        <v>Tooth Extraction</v>
       </c>
       <c r="H4" t="str">
-        <v>2026-07-20T11:30:24.684Z</v>
+        <v>Checked In</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-07-20T18:21:57.834Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-07-20T11:31:07.414Z</v>
+        <v>2026-07-28T12:39:37.024Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-07-20T11:34:36.341Z</v>
+        <v>2026-07-28T12:39:37.024Z</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-07-20T11:34:54.998Z</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>2026-07-20T18:21:57.834Z</v>
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>APP_20260720_0004</v>
+        <v>APP_20260728_0004</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_f6a7b8c9</v>
+        <v>PAT_7a8b9c0d</v>
       </c>
       <c r="C5" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D5" t="str">
-        <v>2026-07-20</v>
+      <c r="D5">
+        <v>4</v>
       </c>
       <c r="E5" t="str">
-        <v>09:30</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F5" t="str">
-        <v>Tooth Filling</v>
+        <v>16:45</v>
       </c>
       <c r="G5" t="str">
-        <v>Completed</v>
+        <v>Wisdom Tooth</v>
       </c>
       <c r="H5" t="str">
-        <v>2026-07-20T11:30:46.036Z</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-07-20T18:21:58.777Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-07-20T11:31:07.983Z</v>
+        <v>2026-07-28T12:38:21.475Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-07-20T11:35:00.481Z</v>
+        <v>2026-07-28T12:35:48.198Z</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-07-20T11:35:49.897Z</v>
+        <v>2026-07-28T12:37:35.642Z</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-07-20T18:21:58.777Z</v>
+        <v>2026-07-28T12:38:21.475Z</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>APP_20260720_0005</v>
+        <v>APP_20260728_0005</v>
       </c>
       <c r="B6" t="str">
-        <v>PAT_1a2b3c4d</v>
+        <v>PAT_c3d4e5f6</v>
       </c>
       <c r="C6" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D6" t="str">
-        <v>2026-07-20</v>
+      <c r="D6">
+        <v>5</v>
       </c>
       <c r="E6" t="str">
-        <v>10:00</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F6" t="str">
-        <v>Tooth Pain</v>
+        <v>17:00</v>
       </c>
       <c r="G6" t="str">
-        <v>Paid</v>
+        <v>Braces Consultation</v>
       </c>
       <c r="H6" t="str">
-        <v>2026-07-20T18:22:12.399Z</v>
+        <v>Checked In</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-07-22T03:37:23.388Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-07-20T18:22:19.485Z</v>
+        <v>2026-07-28T12:37:31.078Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-07-20T18:25:47.544Z</v>
+        <v>2026-07-28T12:37:31.078Z</v>
       </c>
       <c r="L6" t="str">
-        <v>2026-07-20T18:27:21.225Z</v>
+        <v/>
       </c>
       <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>APP_20260721_0006</v>
+        <v>APP_20260728_0006</v>
       </c>
       <c r="B7" t="str">
-        <v>PAT_1a2b3c4d</v>
+        <v>PAT_a1b2c3d4</v>
       </c>
       <c r="C7" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D7" t="str">
-        <v>2026-07-21</v>
+      <c r="D7">
+        <v>6</v>
       </c>
       <c r="E7" t="str">
-        <v>08:00</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F7" t="str">
-        <v>Tooth Extraction</v>
+        <v>17:15</v>
       </c>
       <c r="G7" t="str">
-        <v>Paid</v>
+        <v>Follow-up Visit</v>
       </c>
       <c r="H7" t="str">
-        <v>2026-07-21T03:33:28.093Z</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-07-22T03:37:26.199Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-07-21T03:33:31.367Z</v>
+        <v>2026-07-28T12:37:12.936Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-07-21T03:33:40.296Z</v>
+        <v>2026-07-28T12:34:11.157Z</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-07-21T04:02:46.041Z</v>
+        <v>2026-07-28T12:36:36.427Z</v>
       </c>
       <c r="M7" t="str">
+        <v>2026-07-28T12:37:12.936Z</v>
+      </c>
+      <c r="N7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>APP_20260721_0007</v>
+        <v>APP_20260728_0007</v>
       </c>
       <c r="B8" t="str">
-        <v>PAT_3c4d5e6f</v>
+        <v>PAT_c5d6e7f8</v>
       </c>
       <c r="C8" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D8" t="str">
-        <v>2026-07-21</v>
+      <c r="D8">
+        <v>7</v>
       </c>
       <c r="E8" t="str">
-        <v>08:30</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F8" t="str">
-        <v>Tooth Filling</v>
+        <v>17:30</v>
       </c>
       <c r="G8" t="str">
-        <v>Payment Pending</v>
+        <v>Consultation</v>
       </c>
       <c r="H8" t="str">
-        <v>2026-07-21T03:37:56.886Z</v>
+        <v>In Treatment</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-07-21T08:50:03.166Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-07-21T03:38:24.849Z</v>
+        <v>2026-07-28T12:38:31.382Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-07-21T04:02:59.270Z</v>
+        <v>2026-07-28T12:37:00.874Z</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-07-21T04:04:51.456Z</v>
+        <v>2026-07-28T12:38:31.382Z</v>
       </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>APP_20260721_0008</v>
+        <v>APP_20260728_0008</v>
       </c>
       <c r="B9" t="str">
-        <v>PAT_a1b2c3d4</v>
+        <v>PAT_a3b4c5d6</v>
       </c>
       <c r="C9" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D9" t="str">
-        <v>2026-07-21</v>
+      <c r="D9">
+        <v>8</v>
       </c>
       <c r="E9" t="str">
-        <v>09:00</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F9" t="str">
-        <v>Tooth Extraction</v>
+        <v>17:45</v>
       </c>
       <c r="G9" t="str">
-        <v>Treatment Done</v>
+        <v>Teeth Cleaning</v>
       </c>
       <c r="H9" t="str">
-        <v>2026-07-21T03:38:21.706Z</v>
+        <v>Checked In</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-07-21T08:59:35.503Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-07-21T03:38:26.046Z</v>
+        <v>2026-07-28T12:39:57.582Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-07-21T08:59:25.077Z</v>
+        <v>2026-07-28T12:39:57.582Z</v>
       </c>
       <c r="L9" t="str">
-        <v>2026-07-21T08:59:35.503Z</v>
+        <v/>
       </c>
       <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>APP_20260721_0009</v>
+        <v>APP_20260728_0009</v>
       </c>
       <c r="B10" t="str">
-        <v>PAT_5e6f7a8b</v>
+        <v>PAT_a7b8c9d0</v>
       </c>
       <c r="C10" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D10" t="str">
-        <v>2026-07-21</v>
+      <c r="D10">
+        <v>9</v>
       </c>
       <c r="E10" t="str">
-        <v>09:30</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F10" t="str">
-        <v>Tooth Pain</v>
+        <v>18:00</v>
       </c>
       <c r="G10" t="str">
-        <v>Treatment Done</v>
+        <v>Root Canal Treatment</v>
       </c>
       <c r="H10" t="str">
-        <v>2026-07-21T04:03:37.081Z</v>
+        <v>Checked In</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-07-21T08:59:20.937Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-07-21T04:04:03.598Z</v>
+        <v>2026-07-28T12:39:53.557Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-07-21T08:57:07.014Z</v>
+        <v>2026-07-28T12:39:53.557Z</v>
       </c>
       <c r="L10" t="str">
-        <v>2026-07-21T08:59:20.937Z</v>
+        <v/>
       </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>APP_20260721_0010</v>
+        <v>APP_20260728_0010</v>
       </c>
       <c r="B11" t="str">
-        <v>PAT_2b3c4d5e</v>
+        <v>PAT_7a8b9c0d</v>
       </c>
       <c r="C11" t="str">
         <v>DEN_0001</v>
       </c>
-      <c r="D11" t="str">
-        <v>2026-07-21</v>
+      <c r="D11">
+        <v>10</v>
       </c>
       <c r="E11" t="str">
-        <v>10:00</v>
+        <v>2026-07-28</v>
       </c>
       <c r="F11" t="str">
-        <v>Tooth Extraction</v>
+        <v>18:15</v>
       </c>
       <c r="G11" t="str">
-        <v>Paid</v>
+        <v>Broken Tooth</v>
       </c>
       <c r="H11" t="str">
-        <v>2026-07-21T04:03:57.129Z</v>
+        <v>Checked In</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-07-21T08:59:02.798Z</v>
+        <v>2026-07-28T06:43:23.670Z</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-07-21T04:04:04.468Z</v>
+        <v>2026-07-28T12:39:53.980Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-07-21T04:05:31.745Z</v>
+        <v>2026-07-28T12:39:53.980Z</v>
       </c>
       <c r="L11" t="str">
-        <v>2026-07-21T08:49:44.061Z</v>
+        <v/>
       </c>
       <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>APP_20260728_0011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>PAT_d0e1f2a3</v>
+      </c>
+      <c r="C12" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="F12" t="str">
+        <v>18:30</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Tooth Pain</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Checked In</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2026-07-28T06:43:23.670Z</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-07-28T12:39:54.628Z</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-07-28T12:39:54.628Z</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>APP_20260731_0012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>PAT_1a2b3c4d</v>
+      </c>
+      <c r="C13" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="F13" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Dental Implant - One Unit</v>
+      </c>
+      <c r="H13" t="str">
+        <v>In Treatment</v>
+      </c>
+      <c r="I13" t="str">
+        <v>2026-07-31T07:01:01.770Z</v>
+      </c>
+      <c r="J13" t="str">
+        <v>2026-07-31T07:01:36.291Z</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-07-31T07:01:17.822Z</v>
+      </c>
+      <c r="L13" t="str">
+        <v>2026-07-31T07:01:36.291Z</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1763,761 +2009,10 @@
         <v>installment_number</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>PAY_a84d9f63</v>
-      </c>
-      <c r="B2" t="str">
-        <v>PAT_3c4d5e6f</v>
-      </c>
-      <c r="C2" t="str">
-        <v>TRT_cbe47bfa</v>
-      </c>
-      <c r="D2">
-        <v>15000</v>
-      </c>
-      <c r="E2">
-        <v>15000</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>15000</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K2" t="str">
-        <v>REC-1784547107919</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2026-07-20T11:31:47.988Z</v>
-      </c>
-      <c r="N2" t="str">
-        <v>2026-07-20T11:31:47.988Z</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>PAY_1ff751c8</v>
-      </c>
-      <c r="B3" t="str">
-        <v>PAT_5e6f7a8b</v>
-      </c>
-      <c r="C3" t="str">
-        <v>TRT_e11e5fd7</v>
-      </c>
-      <c r="D3">
-        <v>10000</v>
-      </c>
-      <c r="E3">
-        <v>1000</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1000</v>
-      </c>
-      <c r="H3">
-        <v>9000</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K3" t="str">
-        <v>REC-1784547224285</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2026-07-20T11:33:44.365Z</v>
-      </c>
-      <c r="N3" t="str">
-        <v>2026-07-20T11:33:44.365Z</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PAY_1dbdfb98</v>
-      </c>
-      <c r="B4" t="str">
-        <v>PAT_5e6f7a8b</v>
-      </c>
-      <c r="C4" t="str">
-        <v>TRT_e11e5fd7</v>
-      </c>
-      <c r="D4">
-        <v>10000</v>
-      </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-      <c r="F4">
-        <v>1000</v>
-      </c>
-      <c r="G4">
-        <v>2000</v>
-      </c>
-      <c r="H4">
-        <v>8000</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K4" t="str">
-        <v>REC-1784570891967</v>
-      </c>
-      <c r="L4" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M4" t="str">
-        <v>2026-07-20T18:08:12.039Z</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2026-07-20T18:08:12.039Z</v>
-      </c>
-      <c r="O4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>PAY_88dc9b37</v>
-      </c>
-      <c r="B5" t="str">
-        <v>PAT_5e6f7a8b</v>
-      </c>
-      <c r="C5" t="str">
-        <v>TRT_3bf62a08</v>
-      </c>
-      <c r="D5">
-        <v>10000</v>
-      </c>
-      <c r="E5">
-        <v>500</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>500</v>
-      </c>
-      <c r="H5">
-        <v>9500</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K5" t="str">
-        <v>REC-1784570950188</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M5" t="str">
-        <v>2026-07-20T18:09:10.240Z</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2026-07-20T18:09:10.240Z</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>PAY_4f3d417d</v>
-      </c>
-      <c r="B6" t="str">
-        <v>PAT_f6a7b8c9</v>
-      </c>
-      <c r="C6" t="str">
-        <v>TRT_33dc7abc</v>
-      </c>
-      <c r="D6">
-        <v>2000</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1000</v>
-      </c>
-      <c r="H6">
-        <v>1000</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K6" t="str">
-        <v>REC-1784570958605</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M6" t="str">
-        <v>2026-07-20T18:09:18.656Z</v>
-      </c>
-      <c r="N6" t="str">
-        <v>2026-07-20T18:09:18.656Z</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PAY_a07fc7ad</v>
-      </c>
-      <c r="B7" t="str">
-        <v>PAT_f6a7b8c9</v>
-      </c>
-      <c r="C7" t="str">
-        <v>TRT_33dc7abc</v>
-      </c>
-      <c r="D7">
-        <v>2000</v>
-      </c>
-      <c r="E7">
-        <v>500</v>
-      </c>
-      <c r="F7">
-        <v>1000</v>
-      </c>
-      <c r="G7">
-        <v>1500</v>
-      </c>
-      <c r="H7">
-        <v>500</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K7" t="str">
-        <v>REC-1784570992569</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M7" t="str">
-        <v>2026-07-20T18:09:52.618Z</v>
-      </c>
-      <c r="N7" t="str">
-        <v>2026-07-20T18:09:52.618Z</v>
-      </c>
-      <c r="O7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>PAY_20fada12</v>
-      </c>
-      <c r="B8" t="str">
-        <v>PAT_f6a7b8c9</v>
-      </c>
-      <c r="C8" t="str">
-        <v>TRT_33dc7abc</v>
-      </c>
-      <c r="D8">
-        <v>2000</v>
-      </c>
-      <c r="E8">
-        <v>250</v>
-      </c>
-      <c r="F8">
-        <v>1500</v>
-      </c>
-      <c r="G8">
-        <v>1750</v>
-      </c>
-      <c r="H8">
-        <v>250</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K8" t="str">
-        <v>REC-1784570997376</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M8" t="str">
-        <v>2026-07-20T18:09:57.419Z</v>
-      </c>
-      <c r="N8" t="str">
-        <v>2026-07-20T18:09:57.419Z</v>
-      </c>
-      <c r="O8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>PAY_7d5d43d3</v>
-      </c>
-      <c r="B9" t="str">
-        <v>PAT_f6a7b8c9</v>
-      </c>
-      <c r="C9" t="str">
-        <v>TRT_33dc7abc</v>
-      </c>
-      <c r="D9">
-        <v>2000</v>
-      </c>
-      <c r="E9">
-        <v>125</v>
-      </c>
-      <c r="F9">
-        <v>1750</v>
-      </c>
-      <c r="G9">
-        <v>1875</v>
-      </c>
-      <c r="H9">
-        <v>125</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J9" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K9" t="str">
-        <v>REC-1784571001504</v>
-      </c>
-      <c r="L9" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M9" t="str">
-        <v>2026-07-20T18:10:01.556Z</v>
-      </c>
-      <c r="N9" t="str">
-        <v>2026-07-20T18:10:01.556Z</v>
-      </c>
-      <c r="O9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>PAY_d24cadc5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>PAT_f6a7b8c9</v>
-      </c>
-      <c r="C10" t="str">
-        <v>TRT_33dc7abc</v>
-      </c>
-      <c r="D10">
-        <v>2000</v>
-      </c>
-      <c r="E10">
-        <v>125</v>
-      </c>
-      <c r="F10">
-        <v>1875</v>
-      </c>
-      <c r="G10">
-        <v>2000</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="K10" t="str">
-        <v>REC-1784571004514</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="M10" t="str">
-        <v>2026-07-20T18:10:04.567Z</v>
-      </c>
-      <c r="N10" t="str">
-        <v>2026-07-20T18:10:04.567Z</v>
-      </c>
-      <c r="O10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>PAY_4bf78462</v>
-      </c>
-      <c r="B11" t="str">
-        <v>PAT_1a2b3c4d</v>
-      </c>
-      <c r="C11" t="str">
-        <v>TRT_1fe4635d</v>
-      </c>
-      <c r="D11">
-        <v>1000</v>
-      </c>
-      <c r="E11">
-        <v>500</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>500</v>
-      </c>
-      <c r="H11">
-        <v>500</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="K11" t="str">
-        <v>REC-1784623798778</v>
-      </c>
-      <c r="L11" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M11" t="str">
-        <v>2026-07-21T08:49:58.912Z</v>
-      </c>
-      <c r="N11" t="str">
-        <v>2026-07-21T08:49:58.912Z</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>PAY_c4017c3a</v>
-      </c>
-      <c r="B12" t="str">
-        <v>PAT_3c4d5e6f</v>
-      </c>
-      <c r="C12" t="str">
-        <v>TRT_eca81a5e</v>
-      </c>
-      <c r="D12">
-        <v>2000</v>
-      </c>
-      <c r="E12">
-        <v>500</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>500</v>
-      </c>
-      <c r="H12">
-        <v>1500</v>
-      </c>
-      <c r="I12" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J12" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="K12" t="str">
-        <v>REC-1784623802827</v>
-      </c>
-      <c r="L12" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M12" t="str">
-        <v>2026-07-21T08:50:02.958Z</v>
-      </c>
-      <c r="N12" t="str">
-        <v>2026-07-21T08:50:02.958Z</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>PAY_3fa60634</v>
-      </c>
-      <c r="B13" t="str">
-        <v>PAT_5e6f7a8b</v>
-      </c>
-      <c r="C13" t="str">
-        <v>TRT_3bf62a08</v>
-      </c>
-      <c r="D13">
-        <v>10000</v>
-      </c>
-      <c r="E13">
-        <v>2000</v>
-      </c>
-      <c r="F13">
-        <v>500</v>
-      </c>
-      <c r="G13">
-        <v>2500</v>
-      </c>
-      <c r="H13">
-        <v>7500</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J13" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="K13" t="str">
-        <v>REC-1784623846026</v>
-      </c>
-      <c r="L13" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M13" t="str">
-        <v>2026-07-21T08:50:46.148Z</v>
-      </c>
-      <c r="N13" t="str">
-        <v>2026-07-21T08:50:46.148Z</v>
-      </c>
-      <c r="O13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>PAY_d3749ef6</v>
-      </c>
-      <c r="B14" t="str">
-        <v>PAT_5e6f7a8b</v>
-      </c>
-      <c r="C14" t="str">
-        <v>TRT_3bf62a08</v>
-      </c>
-      <c r="D14">
-        <v>10000</v>
-      </c>
-      <c r="E14">
-        <v>2000</v>
-      </c>
-      <c r="F14">
-        <v>2500</v>
-      </c>
-      <c r="G14">
-        <v>4500</v>
-      </c>
-      <c r="H14">
-        <v>5500</v>
-      </c>
-      <c r="I14" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J14" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="K14" t="str">
-        <v>REC-1784623854245</v>
-      </c>
-      <c r="L14" t="str">
-        <v>Partial</v>
-      </c>
-      <c r="M14" t="str">
-        <v>2026-07-21T08:50:54.371Z</v>
-      </c>
-      <c r="N14" t="str">
-        <v>2026-07-21T08:50:54.371Z</v>
-      </c>
-      <c r="O14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>PAY_4936eff6</v>
-      </c>
-      <c r="B15" t="str">
-        <v>PAT_2b3c4d5e</v>
-      </c>
-      <c r="C15" t="str">
-        <v>TRT_636cda6c</v>
-      </c>
-      <c r="D15">
-        <v>2000</v>
-      </c>
-      <c r="E15">
-        <v>2000</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>2000</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J15" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="K15" t="str">
-        <v>REC-1784624342472</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="M15" t="str">
-        <v>2026-07-21T08:59:02.549Z</v>
-      </c>
-      <c r="N15" t="str">
-        <v>2026-07-21T08:59:02.549Z</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>PAY_e6924a86</v>
-      </c>
-      <c r="B16" t="str">
-        <v>PAT_1a2b3c4d</v>
-      </c>
-      <c r="C16" t="str">
-        <v>TRT_9862be43</v>
-      </c>
-      <c r="D16">
-        <v>10000</v>
-      </c>
-      <c r="E16">
-        <v>10000</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>10000</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J16" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="K16" t="str">
-        <v>REC-1784691443287</v>
-      </c>
-      <c r="L16" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="M16" t="str">
-        <v>2026-07-22T03:37:23.351Z</v>
-      </c>
-      <c r="N16" t="str">
-        <v>2026-07-22T03:37:23.351Z</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>PAY_d708420c</v>
-      </c>
-      <c r="B17" t="str">
-        <v>PAT_1a2b3c4d</v>
-      </c>
-      <c r="C17" t="str">
-        <v>TRT_1fe4635d</v>
-      </c>
-      <c r="D17">
-        <v>1000</v>
-      </c>
-      <c r="E17">
-        <v>500</v>
-      </c>
-      <c r="F17">
-        <v>500</v>
-      </c>
-      <c r="G17">
-        <v>1000</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="str">
-        <v>Cash</v>
-      </c>
-      <c r="J17" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="K17" t="str">
-        <v>REC-1784691446101</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Paid</v>
-      </c>
-      <c r="M17" t="str">
-        <v>2026-07-22T03:37:26.167Z</v>
-      </c>
-      <c r="N17" t="str">
-        <v>2026-07-22T03:37:26.167Z</v>
-      </c>
-      <c r="O17">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2584,6 +2079,87 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>username</v>
+      </c>
+      <c r="D1" t="str">
+        <v>password_hash</v>
+      </c>
+      <c r="E1" t="str">
+        <v>role</v>
+      </c>
+      <c r="F1" t="str">
+        <v>status</v>
+      </c>
+      <c r="G1" t="str">
+        <v>created_at</v>
+      </c>
+      <c r="H1" t="str">
+        <v>updated_at</v>
+      </c>
+      <c r="I1" t="str">
+        <v>email</v>
+      </c>
+      <c r="J1" t="str">
+        <v>password</v>
+      </c>
+      <c r="K1" t="str">
+        <v>phone</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>USR_0001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Chamika Deshan</v>
+      </c>
+      <c r="C2" t="str">
+        <v>chamika</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>Admin</v>
+      </c>
+      <c r="F2" t="str">
+        <v>active</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-07-31T05:19:34.736Z</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-07-31T05:21:21.125Z</v>
+      </c>
+      <c r="I2" t="str">
+        <v>chamika@gmail.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>$2b$10$wx9e6hkzra01s4Tf4sv8.OzzyE/ifK3Ac6v68BVCheOzAhcpMmXVa</v>
+      </c>
+      <c r="K2" t="str">
+        <v>0771234567</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P1"/>
   <sheetData>
     <row r="1">
@@ -2644,9 +2220,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2665,33 +2241,42 @@
         <v>doctor_notes</v>
       </c>
       <c r="F1" t="str">
+        <v>diagnosis</v>
+      </c>
+      <c r="G1" t="str">
+        <v>tooth_number</v>
+      </c>
+      <c r="H1" t="str">
+        <v>treatment_details</v>
+      </c>
+      <c r="I1" t="str">
         <v>treatment_fee</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>prescription</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>next_appointment_date</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>treatment_date</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>created_at</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>updated_at</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TRT_cbe47bfa</v>
+        <v>TRT_bfb0fba7</v>
       </c>
       <c r="B2" t="str">
-        <v>PAT_3c4d5e6f</v>
+        <v>PAT_1a2b3c4d</v>
       </c>
       <c r="C2" t="str">
-        <v>APP_20260720_0001</v>
+        <v>APP_20260728_0001</v>
       </c>
       <c r="D2" t="str">
         <v>DEN_0001</v>
@@ -2699,34 +2284,43 @@
       <c r="E2" t="str">
         <v/>
       </c>
-      <c r="F2">
-        <v>15000</v>
+      <c r="F2" t="str">
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>2026-07-20</v>
+        <v>s</v>
+      </c>
+      <c r="I2">
+        <v>10000</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-07-20T11:31:39.329Z</v>
+        <v/>
       </c>
       <c r="K2" t="str">
-        <v>2026-07-20T11:31:39.329Z</v>
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-07-28T12:34:40.740Z</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-07-28T12:34:40.740Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TRT_e11e5fd7</v>
+        <v>TRT_47a0519c</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_5e6f7a8b</v>
+        <v>PAT_3c4d5e6f</v>
       </c>
       <c r="C3" t="str">
-        <v>APP_20260720_0002</v>
+        <v>APP_20260728_0002</v>
       </c>
       <c r="D3" t="str">
         <v>DEN_0001</v>
@@ -2734,34 +2328,43 @@
       <c r="E3" t="str">
         <v/>
       </c>
-      <c r="F3">
-        <v>10000</v>
+      <c r="F3" t="str">
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-07-20</v>
+        <v>123123</v>
+      </c>
+      <c r="I3">
+        <v>2000</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-07-20T11:33:34.876Z</v>
+        <v/>
       </c>
       <c r="K3" t="str">
-        <v>2026-07-20T11:33:34.876Z</v>
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-07-28T12:36:16.940Z</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-07-28T12:36:16.940Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TRT_3bf62a08</v>
+        <v>TRT_daf9d12d</v>
       </c>
       <c r="B4" t="str">
-        <v>PAT_5e6f7a8b</v>
+        <v>PAT_a1b2c3d4</v>
       </c>
       <c r="C4" t="str">
-        <v>APP_20260720_0003</v>
+        <v>APP_20260728_0006</v>
       </c>
       <c r="D4" t="str">
         <v>DEN_0001</v>
@@ -2769,34 +2372,43 @@
       <c r="E4" t="str">
         <v/>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>u</v>
+      </c>
+      <c r="I4">
         <v>10000</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-07-23</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-07-20</v>
-      </c>
       <c r="J4" t="str">
-        <v>2026-07-20T11:34:54.936Z</v>
+        <v/>
       </c>
       <c r="K4" t="str">
-        <v>2026-07-20T11:34:54.936Z</v>
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-07-28</v>
+      </c>
+      <c r="M4" t="str">
+        <v>2026-07-28T12:37:12.919Z</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-07-28T12:37:12.919Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TRT_33dc7abc</v>
+        <v>TRT_e5a4363f</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_f6a7b8c9</v>
+        <v>PAT_7a8b9c0d</v>
       </c>
       <c r="C5" t="str">
-        <v>APP_20260720_0004</v>
+        <v>APP_20260728_0004</v>
       </c>
       <c r="D5" t="str">
         <v>DEN_0001</v>
@@ -2804,387 +2416,407 @@
       <c r="E5" t="str">
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>;</v>
+      </c>
+      <c r="I5">
         <v>2000</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-07-20</v>
-      </c>
       <c r="J5" t="str">
-        <v>2026-07-20T11:35:49.821Z</v>
+        <v/>
       </c>
       <c r="K5" t="str">
-        <v>2026-07-20T11:35:49.821Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>TRT_9862be43</v>
-      </c>
-      <c r="B6" t="str">
-        <v>PAT_1a2b3c4d</v>
-      </c>
-      <c r="C6" t="str">
-        <v>APP_20260720_0005</v>
-      </c>
-      <c r="D6" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6">
-        <v>10000</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2026-07-20T18:27:21.193Z</v>
-      </c>
-      <c r="K6" t="str">
-        <v>2026-07-20T18:27:21.193Z</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TRT_1fe4635d</v>
-      </c>
-      <c r="B7" t="str">
-        <v>PAT_1a2b3c4d</v>
-      </c>
-      <c r="C7" t="str">
-        <v>APP_20260721_0006</v>
-      </c>
-      <c r="D7" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7">
-        <v>1000</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>2026-07-28</v>
       </c>
-      <c r="I7" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2026-07-21T04:02:46.008Z</v>
-      </c>
-      <c r="K7" t="str">
-        <v>2026-07-21T04:02:46.008Z</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>TRT_eca81a5e</v>
-      </c>
-      <c r="B8" t="str">
-        <v>PAT_3c4d5e6f</v>
-      </c>
-      <c r="C8" t="str">
-        <v>APP_20260721_0007</v>
-      </c>
-      <c r="D8" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8">
-        <v>2000</v>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2026-07-21T04:04:51.412Z</v>
-      </c>
-      <c r="K8" t="str">
-        <v>2026-07-21T04:04:51.412Z</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>TRT_636cda6c</v>
-      </c>
-      <c r="B9" t="str">
-        <v>PAT_2b3c4d5e</v>
-      </c>
-      <c r="C9" t="str">
-        <v>APP_20260721_0010</v>
-      </c>
-      <c r="D9" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9">
-        <v>2000</v>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="J9" t="str">
-        <v>2026-07-21T08:49:43.917Z</v>
-      </c>
-      <c r="K9" t="str">
-        <v>2026-07-21T08:49:43.917Z</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>TRT_10cc3e75</v>
-      </c>
-      <c r="B10" t="str">
-        <v>PAT_5e6f7a8b</v>
-      </c>
-      <c r="C10" t="str">
-        <v>APP_20260721_0009</v>
-      </c>
-      <c r="D10" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10">
-        <v>1000</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="I10" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2026-07-21T08:59:20.843Z</v>
-      </c>
-      <c r="K10" t="str">
-        <v>2026-07-21T08:59:20.843Z</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>TRT_85bc2789</v>
-      </c>
-      <c r="B11" t="str">
-        <v>PAT_a1b2c3d4</v>
-      </c>
-      <c r="C11" t="str">
-        <v>APP_20260721_0008</v>
-      </c>
-      <c r="D11" t="str">
-        <v>DEN_0001</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11">
-        <v>2000</v>
-      </c>
-      <c r="G11" t="str">
-        <v>ki</v>
-      </c>
-      <c r="H11" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="I11" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2026-07-21T08:59:35.184Z</v>
-      </c>
-      <c r="K11" t="str">
-        <v>2026-07-21T08:59:35.184Z</v>
+      <c r="M5" t="str">
+        <v>2026-07-28T12:38:21.452Z</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-07-28T12:38:21.452Z</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:E21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>id</v>
       </c>
       <c r="B1" t="str">
-        <v>name</v>
+        <v>treatment_name</v>
       </c>
       <c r="C1" t="str">
-        <v>username</v>
+        <v>fee</v>
       </c>
       <c r="D1" t="str">
-        <v>password_hash</v>
+        <v>created_at</v>
       </c>
       <c r="E1" t="str">
-        <v>role</v>
-      </c>
-      <c r="F1" t="str">
-        <v>status</v>
-      </c>
-      <c r="G1" t="str">
-        <v>created_at</v>
-      </c>
-      <c r="H1" t="str">
         <v>updated_at</v>
-      </c>
-      <c r="I1" t="str">
-        <v>email</v>
-      </c>
-      <c r="J1" t="str">
-        <v>password</v>
-      </c>
-      <c r="K1" t="str">
-        <v>phone</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>USR_5174ffd5</v>
+        <v>CT_0001</v>
       </c>
       <c r="B2" t="str">
-        <v>Chamika Deshan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>chamika</v>
+        <v>Root Canal Treatment</v>
+      </c>
+      <c r="C2">
+        <v>20000</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>2026-07-30T16:15:00.000Z</v>
       </c>
       <c r="E2" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Active</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-07-21T05:34:03.802Z</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-07-21T05:34:03.802Z</v>
-      </c>
-      <c r="I2" t="str">
-        <v>chamika@gmail.com</v>
-      </c>
-      <c r="J2" t="str">
-        <v>$2b$12$A487FCpgu3hHQDasupKbSeElbj569vzDBoABBo3NiGbCT.2eumVOu</v>
-      </c>
-      <c r="K2" t="str">
-        <v>0771234567</v>
+        <v>2026-07-30T16:15:00.000Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>USR_efbf7fd0</v>
+        <v>CT_0002</v>
       </c>
       <c r="B3" t="str">
-        <v>Chamika Jayasingha</v>
-      </c>
-      <c r="C3" t="str">
-        <v>chamik97</v>
+        <v>Fixed Appliance - Upper</v>
+      </c>
+      <c r="C3">
+        <v>75000</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>2026-07-30T16:15:00.000Z</v>
       </c>
       <c r="E3" t="str">
-        <v>Receptionist</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Active</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-07-21T08:17:18.797Z</v>
-      </c>
-      <c r="H3" t="str">
-        <v>2026-07-21T08:17:18.797Z</v>
-      </c>
-      <c r="I3" t="str">
-        <v>deshjayasingha@gmail.com</v>
-      </c>
-      <c r="J3" t="str">
-        <v>$2b$12$cU.kTJ/7LPr4bN0G0HNcKuPAmJ4QYwTNR.MoL6FnHoJPuBiPrMLlS</v>
-      </c>
-      <c r="K3" t="str">
-        <v>+94718553224</v>
+        <v>2026-07-30T16:15:00.000Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>USR_6d004512</v>
+        <v>CT_0003</v>
       </c>
       <c r="B4" t="str">
-        <v>Cashier</v>
-      </c>
-      <c r="C4" t="str">
-        <v>cashier</v>
+        <v>Permanent Filling</v>
+      </c>
+      <c r="C4">
+        <v>5000</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
       </c>
       <c r="E4" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Active</v>
-      </c>
-      <c r="G4" t="str">
-        <v>2026-07-21T08:19:09.205Z</v>
-      </c>
-      <c r="H4" t="str">
-        <v>2026-07-21T08:19:09.205Z</v>
-      </c>
-      <c r="I4" t="str">
-        <v>desh3jayasingha@gmail.com</v>
-      </c>
-      <c r="J4" t="str">
-        <v>$2b$12$BhnME1OBWl2xguGbjdKA5esVN51OsdJTALc5dzks/c8Z0DZaceXQi</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>CT_0004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Tooth Extraction</v>
+      </c>
+      <c r="C5">
+        <v>3000</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>CT_0005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Surgical Extraction</v>
+      </c>
+      <c r="C6">
+        <v>20000</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CT_0006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Temporary Filling</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CT_0007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Removable Appliance</v>
+      </c>
+      <c r="C8">
+        <v>30000</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CT_0008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Dental Implant - One Unit</v>
+      </c>
+      <c r="C9">
+        <v>150000</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CT_0009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>GIC Filling</v>
+      </c>
+      <c r="C10">
+        <v>5000</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CT_0010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Composite Filling</v>
+      </c>
+      <c r="C11">
+        <v>6000</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CT_0011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Scaling and Polishing</v>
+      </c>
+      <c r="C12">
+        <v>5000</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CT_0012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>RPD Basic</v>
+      </c>
+      <c r="C13">
+        <v>5000</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>CT_0013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>RPD Add Tooth</v>
+      </c>
+      <c r="C14">
+        <v>3000</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CT_0014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Flexible Partial Denture</v>
+      </c>
+      <c r="C15">
+        <v>15000</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CT_0015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Flexible Denture Add Tooth</v>
+      </c>
+      <c r="C16">
+        <v>5000</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CT_0016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Full Basic Denture - Upper or Lower</v>
+      </c>
+      <c r="C17">
+        <v>30000</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CT_0017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Full Basic Denture - Upper and Lower</v>
+      </c>
+      <c r="C18">
+        <v>60000</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>CT_0018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Flexible Full Denture - Upper or Lower</v>
+      </c>
+      <c r="C19">
+        <v>40000</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>CT_0019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Flexible Full Denture - Upper and Lower</v>
+      </c>
+      <c r="C20">
+        <v>80000</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>CT_0020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Drugs</v>
+      </c>
+      <c r="C21">
+        <v>500</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-07-30T16:15:00.000Z</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/dental_clinic_database.xlsx
+++ b/data/dental_clinic_database.xlsx
@@ -12,7 +12,9 @@
     <sheet name="DailyQueue" sheetId="7" r:id="rId7"/>
     <sheet name="Treatments" sheetId="8" r:id="rId8"/>
     <sheet name="Common_Treatments" sheetId="9" r:id="rId9"/>
-    <sheet name="Sheet1" sheetId="10" r:id="rId10"/>
+    <sheet name="Drugs" sheetId="10" r:id="rId10"/>
+    <sheet name="InWaiting" sheetId="11" r:id="rId11"/>
+    <sheet name="Locations" sheetId="12" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
@@ -406,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:L27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,9 +436,15 @@
         <v>allergies</v>
       </c>
       <c r="I1" t="str">
+        <v>location</v>
+      </c>
+      <c r="J1" t="str">
+        <v>distance</v>
+      </c>
+      <c r="K1" t="str">
         <v>created_at</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>updated_at</v>
       </c>
     </row>
@@ -466,9 +474,15 @@
         <v/>
       </c>
       <c r="I2" t="str">
+        <v>Palatuwa</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2" t="str">
         <v>2026-07-01T08:15:20.000Z</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>2026-07-01T08:15:20.000Z</v>
       </c>
     </row>
@@ -498,9 +512,15 @@
         <v>Penicillin</v>
       </c>
       <c r="I3" t="str">
+        <v>Godagama</v>
+      </c>
+      <c r="J3">
+        <v>4.5</v>
+      </c>
+      <c r="K3" t="str">
         <v>2026-07-02T09:22:14.000Z</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>2026-07-02T09:22:14.000Z</v>
       </c>
     </row>
@@ -530,9 +550,15 @@
         <v/>
       </c>
       <c r="I4" t="str">
+        <v>Kirimatimulla</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4" t="str">
         <v>2026-07-03T10:30:05.000Z</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>2026-07-03T10:30:05.000Z</v>
       </c>
     </row>
@@ -562,9 +588,15 @@
         <v/>
       </c>
       <c r="I5" t="str">
+        <v>Thelijjawila</v>
+      </c>
+      <c r="J5">
+        <v>10.5</v>
+      </c>
+      <c r="K5" t="str">
         <v>2026-07-04T11:45:33.000Z</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>2026-07-04T11:45:33.000Z</v>
       </c>
     </row>
@@ -594,9 +626,15 @@
         <v/>
       </c>
       <c r="I6" t="str">
+        <v>Kekandura</v>
+      </c>
+      <c r="J6">
+        <v>11.5</v>
+      </c>
+      <c r="K6" t="str">
         <v>2026-07-05T07:20:48.000Z</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
         <v>2026-07-05T07:20:48.000Z</v>
       </c>
     </row>
@@ -607,29 +645,35 @@
       <c r="B7" t="str">
         <v>Amanda Rodrigo</v>
       </c>
-      <c r="C7">
-        <v>707890123</v>
+      <c r="C7" t="str">
+        <v>0707890123</v>
       </c>
       <c r="D7">
         <v>29</v>
       </c>
       <c r="E7" t="str">
-        <v>Female</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>Kalutara</v>
-      </c>
-      <c r="G7" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>Peanuts</v>
+        <v/>
       </c>
       <c r="I7" t="str">
+        <v>Dewundara</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7" t="str">
         <v>2026-07-06T12:10:19.000Z</v>
       </c>
-      <c r="J7" t="str">
-        <v>2026-07-06T12:10:19.000Z</v>
+      <c r="L7" t="str">
+        <v>2026-08-05T11:59:49.457Z</v>
       </c>
     </row>
     <row r="8">
@@ -658,9 +702,15 @@
         <v/>
       </c>
       <c r="I8" t="str">
+        <v>Hiththatiya</v>
+      </c>
+      <c r="J8">
+        <v>1.5</v>
+      </c>
+      <c r="K8" t="str">
         <v>2026-07-07T13:25:41.000Z</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
         <v>2026-07-07T13:25:41.000Z</v>
       </c>
     </row>
@@ -690,9 +740,15 @@
         <v>Aspirin</v>
       </c>
       <c r="I9" t="str">
+        <v>Wewahamanduwa</v>
+      </c>
+      <c r="J9">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="str">
         <v>2026-07-08T14:40:16.000Z</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
         <v>2026-07-08T14:40:16.000Z</v>
       </c>
     </row>
@@ -722,9 +778,15 @@
         <v/>
       </c>
       <c r="I10" t="str">
+        <v>Palatuwa</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10" t="str">
         <v>2026-07-09T08:35:28.000Z</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
         <v>2026-07-09T08:35:28.000Z</v>
       </c>
     </row>
@@ -754,9 +816,15 @@
         <v/>
       </c>
       <c r="I11" t="str">
+        <v>Godagama</v>
+      </c>
+      <c r="J11">
+        <v>4.5</v>
+      </c>
+      <c r="K11" t="str">
         <v>2026-07-10T09:50:37.000Z</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
         <v>2026-07-10T09:50:37.000Z</v>
       </c>
     </row>
@@ -786,9 +854,15 @@
         <v/>
       </c>
       <c r="I12" t="str">
+        <v>Kirimatimulla</v>
+      </c>
+      <c r="J12">
+        <v>9</v>
+      </c>
+      <c r="K12" t="str">
         <v>2026-07-11T10:05:52.000Z</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
         <v>2026-07-11T10:05:52.000Z</v>
       </c>
     </row>
@@ -818,9 +892,15 @@
         <v>Seafood</v>
       </c>
       <c r="I13" t="str">
+        <v>Thelijjawila</v>
+      </c>
+      <c r="J13">
+        <v>10.5</v>
+      </c>
+      <c r="K13" t="str">
         <v>2026-07-12T11:18:44.000Z</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
         <v>2026-07-12T11:18:44.000Z</v>
       </c>
     </row>
@@ -850,9 +930,15 @@
         <v/>
       </c>
       <c r="I14" t="str">
+        <v>Kekandura</v>
+      </c>
+      <c r="J14">
+        <v>11.5</v>
+      </c>
+      <c r="K14" t="str">
         <v>2026-07-13T12:32:10.000Z</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
         <v>2026-07-13T12:32:10.000Z</v>
       </c>
     </row>
@@ -863,29 +949,35 @@
       <c r="B15" t="str">
         <v>Ishara Herath</v>
       </c>
-      <c r="C15">
-        <v>705678902</v>
+      <c r="C15" t="str">
+        <v>0705678902</v>
       </c>
       <c r="D15">
         <v>40</v>
       </c>
       <c r="E15" t="str">
-        <v>Female</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>Badulla</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Local anaesthetic</v>
+        <v/>
       </c>
       <c r="I15" t="str">
+        <v>Dewundara</v>
+      </c>
+      <c r="J15">
+        <v>8</v>
+      </c>
+      <c r="K15" t="str">
         <v>2026-07-14T13:47:26.000Z</v>
       </c>
-      <c r="J15" t="str">
-        <v>2026-07-14T13:47:26.000Z</v>
+      <c r="L15" t="str">
+        <v>2026-08-05T12:09:23.546Z</v>
       </c>
     </row>
     <row r="16">
@@ -914,9 +1006,15 @@
         <v/>
       </c>
       <c r="I16" t="str">
+        <v>Hiththatiya</v>
+      </c>
+      <c r="J16">
+        <v>1.5</v>
+      </c>
+      <c r="K16" t="str">
         <v>2026-07-15T14:55:09.000Z</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
         <v>2026-07-15T14:55:09.000Z</v>
       </c>
     </row>
@@ -946,9 +1044,15 @@
         <v>Dust</v>
       </c>
       <c r="I17" t="str">
+        <v>Wewahamanduwa</v>
+      </c>
+      <c r="J17">
+        <v>3.3</v>
+      </c>
+      <c r="K17" t="str">
         <v>2026-07-16T06:10:31.000Z</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
         <v>2026-07-16T06:10:31.000Z</v>
       </c>
     </row>
@@ -978,9 +1082,15 @@
         <v/>
       </c>
       <c r="I18" t="str">
+        <v>Walgama</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18" t="str">
         <v>2026-07-16T06:18:42.000Z</v>
       </c>
-      <c r="J18" t="str">
+      <c r="L18" t="str">
         <v>2026-07-16T06:18:42.000Z</v>
       </c>
     </row>
@@ -1010,9 +1120,15 @@
         <v/>
       </c>
       <c r="I19" t="str">
+        <v>Pamburana</v>
+      </c>
+      <c r="J19">
+        <v>2</v>
+      </c>
+      <c r="K19" t="str">
         <v>2026-07-16T06:24:15.000Z</v>
       </c>
-      <c r="J19" t="str">
+      <c r="L19" t="str">
         <v>2026-07-16T06:24:15.000Z</v>
       </c>
     </row>
@@ -1042,9 +1158,15 @@
         <v/>
       </c>
       <c r="I20" t="str">
+        <v>Kamburugamuwa</v>
+      </c>
+      <c r="J20">
+        <v>5.5</v>
+      </c>
+      <c r="K20" t="str">
         <v>2026-07-16T06:31:50.000Z</v>
       </c>
-      <c r="J20" t="str">
+      <c r="L20" t="str">
         <v>2026-07-16T06:31:50.000Z</v>
       </c>
     </row>
@@ -1055,29 +1177,35 @@
       <c r="B21" t="str">
         <v>Imesha Lakmali</v>
       </c>
-      <c r="C21">
-        <v>761234568</v>
+      <c r="C21" t="str">
+        <v>0761234568</v>
       </c>
       <c r="D21">
         <v>43</v>
       </c>
       <c r="E21" t="str">
-        <v>Female</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>Kalutara</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
       </c>
       <c r="H21" t="str">
-        <v>Eggs</v>
+        <v/>
       </c>
       <c r="I21" t="str">
+        <v>Nupe</v>
+      </c>
+      <c r="J21">
+        <v>1.5</v>
+      </c>
+      <c r="K21" t="str">
         <v>2026-07-16T06:40:12.000Z</v>
       </c>
-      <c r="J21" t="str">
-        <v>2026-07-16T06:40:12.000Z</v>
+      <c r="L21" t="str">
+        <v>2026-08-05T12:01:40.821Z</v>
       </c>
     </row>
     <row r="22">
@@ -1106,9 +1234,15 @@
         <v/>
       </c>
       <c r="I22" t="str">
+        <v>Polhena</v>
+      </c>
+      <c r="J22">
+        <v>3</v>
+      </c>
+      <c r="K22" t="str">
         <v>2026-07-16T06:48:27.000Z</v>
       </c>
-      <c r="J22" t="str">
+      <c r="L22" t="str">
         <v>2026-07-16T06:48:27.000Z</v>
       </c>
     </row>
@@ -1138,9 +1272,15 @@
         <v>Milk</v>
       </c>
       <c r="I23" t="str">
+        <v>Thalpawila</v>
+      </c>
+      <c r="J23">
+        <v>7.7</v>
+      </c>
+      <c r="K23" t="str">
         <v>2026-07-16T06:55:34.000Z</v>
       </c>
-      <c r="J23" t="str">
+      <c r="L23" t="str">
         <v>2026-07-16T06:55:34.000Z</v>
       </c>
     </row>
@@ -1170,9 +1310,15 @@
         <v/>
       </c>
       <c r="I24" t="str">
+        <v>Akuressa</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
+      <c r="K24" t="str">
         <v>2026-07-16T07:02:46.000Z</v>
       </c>
-      <c r="J24" t="str">
+      <c r="L24" t="str">
         <v>2026-07-16T07:02:46.000Z</v>
       </c>
     </row>
@@ -1183,29 +1329,35 @@
       <c r="B25" t="str">
         <v>Kavindi Rajapaksha</v>
       </c>
-      <c r="C25">
-        <v>725678903</v>
+      <c r="C25" t="str">
+        <v>0725678903</v>
       </c>
       <c r="D25">
         <v>32</v>
       </c>
       <c r="E25" t="str">
-        <v>Female</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>Kegalle</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
       </c>
       <c r="H25" t="str">
-        <v>Sulfa drugs</v>
+        <v/>
       </c>
       <c r="I25" t="str">
+        <v>Thalpawila</v>
+      </c>
+      <c r="J25">
+        <v>7.7</v>
+      </c>
+      <c r="K25" t="str">
         <v>2026-07-16T07:11:29.000Z</v>
       </c>
-      <c r="J25" t="str">
-        <v>2026-07-16T07:11:29.000Z</v>
+      <c r="L25" t="str">
+        <v>2026-08-05T15:53:19.427Z</v>
       </c>
     </row>
     <row r="26">
@@ -1234,21 +1386,27 @@
         <v/>
       </c>
       <c r="I26" t="str">
+        <v>Akuressa</v>
+      </c>
+      <c r="J26">
+        <v>20</v>
+      </c>
+      <c r="K26" t="str">
         <v>2026-07-16T07:20:18.000Z</v>
       </c>
-      <c r="J26" t="str">
+      <c r="L26" t="str">
         <v>2026-07-16T07:20:18.000Z</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>PAT_104d77f7</v>
+        <v>PAT_b605a8bf</v>
       </c>
       <c r="B27" t="str">
-        <v>new</v>
+        <v>Chamika Jayasingha</v>
       </c>
       <c r="C27" t="str">
-        <v>0771234560</v>
+        <v>0718553224</v>
       </c>
       <c r="D27" t="str">
         <v/>
@@ -1259,66 +1417,449 @@
       <c r="F27" t="str">
         <v/>
       </c>
-      <c r="G27" t="b">
-        <v>1</v>
+      <c r="G27" t="str">
+        <v xml:space="preserve"> </v>
       </c>
       <c r="H27" t="str">
-        <v>jjj</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="I27" t="str">
-        <v>2026-07-27T17:10:16.792Z</v>
-      </c>
-      <c r="J27" t="str">
-        <v>2026-07-27T17:10:16.792Z</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>PAT_a087a411</v>
-      </c>
-      <c r="B28" t="str">
-        <v>new1</v>
-      </c>
-      <c r="C28" t="str">
-        <v>0715555000</v>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" t="str">
-        <v>ffjgk</v>
-      </c>
-      <c r="I28" t="str">
-        <v>2026-07-28T06:08:54.377Z</v>
-      </c>
-      <c r="J28" t="str">
-        <v>2026-07-28T06:08:54.377Z</v>
+        <v>Hiththatiya</v>
+      </c>
+      <c r="J27">
+        <v>1.5</v>
+      </c>
+      <c r="K27" t="str">
+        <v>2026-08-05T19:17:53.702Z</v>
+      </c>
+      <c r="L27" t="str">
+        <v>2026-08-05T19:17:53.702Z</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L27"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:B18"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DRG_0001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Amoxicillin 250mg</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DRG_0002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Metronidazole</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DRG_0003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Phenoxymethylpenicillin</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DRG_0004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Azithromycin</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DRG_0005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Clindamycin</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DRG_0006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Paracetamol</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DRG_0007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Ibuprofen</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DRG_0008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Diclofenac Sodium</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>DRG_0009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Chlorhexidine Gluconate</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>DRG_0010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Benzydamine Hydrochloride</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>DRG_0011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Miconazole</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>DRG_0012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Nystatin</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>DRG_0013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Triamcinolone Acetonide</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>DRG_0014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sodium Fluoride Toothpaste</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>DRG_0015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sodium Fluoride Mouth Rinse</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>DRG_0016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Amoxicillin 500mg</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>DRG_0017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>cfghjkl</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>start_time</v>
+      </c>
+      <c r="C1" t="str">
+        <v>end_time</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>APP_20260805_0001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-08-05T18:02:31.846Z</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2026-08-05 23:34:17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>APP_20260805_0002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-08-05T18:03:12.097Z</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-08-05 23:34:19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>APP_20260806_0014</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-08-05T19:20:20.653Z</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-08-06 00:59:38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>APP_20260806_0008</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-08-05T19:20:22.347Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>APP_20260806_0016</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-08-05T19:20:24.304Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>location</v>
+      </c>
+      <c r="C1" t="str">
+        <v>distance_km</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>LOC_0001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Palatuwa</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>LOC_0002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Godagama</v>
+      </c>
+      <c r="C3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>LOC_0003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Kirimatimulla</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LOC_0004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Thelijjawila</v>
+      </c>
+      <c r="C5">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LOC_0005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Kekandura</v>
+      </c>
+      <c r="C6">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LOC_0006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Dewundara</v>
+      </c>
+      <c r="C7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LOC_0007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Hiththatiya</v>
+      </c>
+      <c r="C8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LOC_0008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Wewahamanduwa</v>
+      </c>
+      <c r="C9">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LOC_0009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Walgama</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LOC_0010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Pamburana</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LOC_0011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Kamburugamuwa</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LOC_0012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Nupe</v>
+      </c>
+      <c r="C13">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LOC_0013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Polhena</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LOC_0014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Thalpawila</v>
+      </c>
+      <c r="C15">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LOC_0015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Akuressa</v>
+      </c>
+      <c r="C16">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1377,7 +1918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1419,13 +1960,10 @@
       <c r="M1" t="str">
         <v>treatment_completed_at</v>
       </c>
-      <c r="N1" t="str">
-        <v>completed_at</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>APP_20260728_0001</v>
+        <v>APP_20260805_0001</v>
       </c>
       <c r="B2" t="str">
         <v>PAT_1a2b3c4d</v>
@@ -1437,42 +1975,39 @@
         <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="F2" t="str">
         <v>16:00</v>
       </c>
       <c r="G2" t="str">
-        <v>Dental Check-up</v>
+        <v>GIC Filling</v>
       </c>
       <c r="H2" t="str">
-        <v>Treatment Done</v>
+        <v>Checked In</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T17:58:59.366Z</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-07-28T12:34:40.757Z</v>
+        <v>2026-08-05T18:01:59.159Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-07-28T12:33:31.509Z</v>
+        <v>2026-08-05T18:01:59.159Z</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-07-28T12:34:22.179Z</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-28T12:34:40.757Z</v>
-      </c>
-      <c r="N2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>APP_20260728_0002</v>
+        <v>APP_20260805_0002</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_3c4d5e6f</v>
+        <v>PAT_2b3c4d5e</v>
       </c>
       <c r="C3" t="str">
         <v>DEN_0001</v>
@@ -1481,39 +2016,36 @@
         <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="F3" t="str">
-        <v>16:15</v>
+        <v>16:25</v>
       </c>
       <c r="G3" t="str">
-        <v>Tooth Pain</v>
+        <v>Temporary Filling</v>
       </c>
       <c r="H3" t="str">
-        <v>Treatment Done</v>
+        <v>Checked In</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:00:05.446Z</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-07-28T12:36:16.971Z</v>
+        <v>2026-08-05T18:02:23.965Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-07-28T12:33:34.362Z</v>
+        <v>2026-08-05T18:02:23.965Z</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-07-28T12:34:52.401Z</v>
+        <v/>
       </c>
       <c r="M3" t="str">
-        <v>2026-07-28T12:36:16.971Z</v>
-      </c>
-      <c r="N3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>APP_20260728_0003</v>
+        <v>APP_20260805_0003</v>
       </c>
       <c r="B4" t="str">
         <v>PAT_5e6f7a8b</v>
@@ -1525,42 +2057,39 @@
         <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="F4" t="str">
-        <v>16:30</v>
+        <v>16:40</v>
       </c>
       <c r="G4" t="str">
-        <v>Tooth Extraction</v>
+        <v>RPD Add Tooth</v>
       </c>
       <c r="H4" t="str">
-        <v>Checked In</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:00:14.310Z</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-07-28T12:39:37.024Z</v>
+        <v>2026-08-05T18:01:35.598Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-07-28T12:39:37.024Z</v>
+        <v>2026-08-05T18:00:41.547Z</v>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>2026-08-05T18:01:13.019Z</v>
       </c>
       <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v/>
+        <v>2026-08-05T18:01:35.598Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>APP_20260728_0004</v>
+        <v>APP_20260805_0004</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_7a8b9c0d</v>
+        <v>PAT_b4c5d6e7</v>
       </c>
       <c r="C5" t="str">
         <v>DEN_0001</v>
@@ -1569,42 +2098,39 @@
         <v>4</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="F5" t="str">
-        <v>16:45</v>
+        <v>16:55</v>
       </c>
       <c r="G5" t="str">
-        <v>Wisdom Tooth</v>
+        <v>Flexible Denture Add Tooth</v>
       </c>
       <c r="H5" t="str">
         <v>Treatment Done</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:00:25.178Z</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-07-28T12:38:21.475Z</v>
+        <v>2026-08-05T18:08:31.189Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-07-28T12:35:48.198Z</v>
+        <v>2026-08-05T18:02:13.476Z</v>
       </c>
       <c r="L5" t="str">
-        <v>2026-07-28T12:37:35.642Z</v>
+        <v>2026-08-05T18:04:10.860Z</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-07-28T12:38:21.475Z</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
+        <v>2026-08-05T18:08:31.189Z</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>APP_20260728_0005</v>
+        <v>APP_20260805_0005</v>
       </c>
       <c r="B6" t="str">
-        <v>PAT_c3d4e5f6</v>
+        <v>PAT_9c0d1e2f</v>
       </c>
       <c r="C6" t="str">
         <v>DEN_0001</v>
@@ -1613,354 +2139,494 @@
         <v>5</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="F6" t="str">
-        <v>17:00</v>
+        <v>17:10</v>
       </c>
       <c r="G6" t="str">
-        <v>Braces Consultation</v>
+        <v>RPD Add Tooth</v>
       </c>
       <c r="H6" t="str">
-        <v>Checked In</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I6" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:00:33.739Z</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-07-28T12:37:31.078Z</v>
+        <v>2026-08-05T18:02:46.613Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-07-28T12:37:31.078Z</v>
+        <v>2026-08-05T18:01:06.544Z</v>
       </c>
       <c r="L6" t="str">
-        <v/>
+        <v>2026-08-05T18:02:06.193Z</v>
       </c>
       <c r="M6" t="str">
-        <v/>
-      </c>
-      <c r="N6" t="str">
-        <v/>
+        <v>2026-08-05T18:02:46.613Z</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>APP_20260728_0006</v>
+        <v>APP_20260806_0006</v>
       </c>
       <c r="B7" t="str">
-        <v>PAT_a1b2c3d4</v>
+        <v>PAT_1a2b3c4d</v>
       </c>
       <c r="C7" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F7" t="str">
-        <v>17:15</v>
+        <v>16:00</v>
       </c>
       <c r="G7" t="str">
-        <v>Follow-up Visit</v>
+        <v>Composite Filling</v>
       </c>
       <c r="H7" t="str">
         <v>Treatment Done</v>
       </c>
       <c r="I7" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:42:04.208Z</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-07-28T12:37:12.936Z</v>
+        <v>2026-08-05T19:24:42.060Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-07-28T12:34:11.157Z</v>
+        <v>2026-08-05T18:56:58.328Z</v>
       </c>
       <c r="L7" t="str">
-        <v>2026-07-28T12:36:36.427Z</v>
+        <v>2026-08-05T18:57:07.995Z</v>
       </c>
       <c r="M7" t="str">
-        <v>2026-07-28T12:37:12.936Z</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
+        <v>2026-08-05T19:24:42.060Z</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>APP_20260728_0007</v>
+        <v>APP_20260806_0007</v>
       </c>
       <c r="B8" t="str">
-        <v>PAT_c5d6e7f8</v>
+        <v>PAT_3c4d5e6f</v>
       </c>
       <c r="C8" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F8" t="str">
-        <v>17:30</v>
+        <v>16:15</v>
       </c>
       <c r="G8" t="str">
-        <v>Consultation</v>
+        <v>Drugs</v>
       </c>
       <c r="H8" t="str">
-        <v>In Treatment</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I8" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:42:39.819Z</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-07-28T12:38:31.382Z</v>
+        <v>2026-08-06T00:04:56.370Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-07-28T12:37:00.874Z</v>
+        <v>2026-08-05T23:59:59.383Z</v>
       </c>
       <c r="L8" t="str">
-        <v>2026-07-28T12:38:31.382Z</v>
+        <v>2026-08-06T00:00:09.431Z</v>
       </c>
       <c r="M8" t="str">
-        <v/>
-      </c>
-      <c r="N8" t="str">
-        <v/>
+        <v>2026-08-06T00:04:56.370Z</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>APP_20260728_0008</v>
+        <v>APP_20260806_0008</v>
       </c>
       <c r="B9" t="str">
-        <v>PAT_a3b4c5d6</v>
+        <v>PAT_3c4d5e6f</v>
       </c>
       <c r="C9" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F9" t="str">
-        <v>17:45</v>
+        <v>16:30</v>
       </c>
       <c r="G9" t="str">
-        <v>Teeth Cleaning</v>
+        <v>Flexible Denture Add Tooth</v>
       </c>
       <c r="H9" t="str">
         <v>Checked In</v>
       </c>
       <c r="I9" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:44:11.934Z</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-07-28T12:39:57.582Z</v>
+        <v>2026-08-05T19:20:04.407Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-07-28T12:39:57.582Z</v>
+        <v>2026-08-05T19:20:04.407Z</v>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
-        <v/>
-      </c>
-      <c r="N9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>APP_20260728_0009</v>
+        <v>APP_20260806_0009</v>
       </c>
       <c r="B10" t="str">
-        <v>PAT_a7b8c9d0</v>
+        <v>PAT_5e6f7a8b</v>
       </c>
       <c r="C10" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F10" t="str">
-        <v>18:00</v>
+        <v>16:45</v>
       </c>
       <c r="G10" t="str">
-        <v>Root Canal Treatment</v>
+        <v>Flexible Denture Add Tooth</v>
       </c>
       <c r="H10" t="str">
-        <v>Checked In</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I10" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:45:01.684Z</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-07-28T12:39:53.557Z</v>
+        <v>2026-08-05T19:46:37.099Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-07-28T12:39:53.557Z</v>
+        <v>2026-08-05T18:57:58.484Z</v>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>2026-08-05T19:46:17.132Z</v>
       </c>
       <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
+        <v>2026-08-05T19:46:37.099Z</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>APP_20260728_0010</v>
+        <v>APP_20260806_0010</v>
       </c>
       <c r="B11" t="str">
-        <v>PAT_7a8b9c0d</v>
+        <v>PAT_8b9c0d1e</v>
       </c>
       <c r="C11" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F11" t="str">
-        <v>18:15</v>
+        <v>17:00</v>
       </c>
       <c r="G11" t="str">
-        <v>Broken Tooth</v>
+        <v>Flexible Denture Add Tooth</v>
       </c>
       <c r="H11" t="str">
-        <v>Checked In</v>
+        <v>Treatment Done</v>
       </c>
       <c r="I11" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:46:05.612Z</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-07-28T12:39:53.980Z</v>
+        <v>2026-08-06T00:51:49.057Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-07-28T12:39:53.980Z</v>
+        <v>2026-08-06T00:00:01.645Z</v>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>2026-08-06T00:51:07.419Z</v>
       </c>
       <c r="M11" t="str">
-        <v/>
-      </c>
-      <c r="N11" t="str">
-        <v/>
+        <v>2026-08-06T00:51:49.057Z</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>APP_20260728_0011</v>
+        <v>APP_20260806_0011</v>
       </c>
       <c r="B12" t="str">
-        <v>PAT_d0e1f2a3</v>
+        <v>PAT_c3d4e5f6</v>
       </c>
       <c r="C12" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F12" t="str">
-        <v>18:30</v>
+        <v>17:15</v>
       </c>
       <c r="G12" t="str">
-        <v>Tooth Pain</v>
+        <v>Temporary Filling</v>
       </c>
       <c r="H12" t="str">
         <v>Checked In</v>
       </c>
       <c r="I12" t="str">
-        <v>2026-07-28T06:43:23.670Z</v>
+        <v>2026-08-05T18:47:07.040Z</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-07-28T12:39:54.628Z</v>
+        <v>2026-08-06T00:00:04.103Z</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-07-28T12:39:54.628Z</v>
+        <v>2026-08-06T00:00:04.103Z</v>
       </c>
       <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
-        <v/>
-      </c>
-      <c r="N12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>APP_20260731_0012</v>
+        <v>APP_20260806_0012</v>
       </c>
       <c r="B13" t="str">
-        <v>PAT_1a2b3c4d</v>
+        <v>PAT_a1b2c3d4</v>
       </c>
       <c r="C13" t="str">
         <v>DEN_0001</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-31</v>
+        <v>2026-08-06</v>
       </c>
       <c r="F13" t="str">
-        <v>08:00</v>
+        <v>17:30</v>
       </c>
       <c r="G13" t="str">
-        <v>Dental Implant - One Unit</v>
+        <v>Drugs</v>
       </c>
       <c r="H13" t="str">
         <v>In Treatment</v>
       </c>
       <c r="I13" t="str">
-        <v>2026-07-31T07:01:01.770Z</v>
+        <v>2026-08-05T18:47:33.488Z</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-07-31T07:01:36.291Z</v>
+        <v>2026-08-06T00:55:47.704Z</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-07-31T07:01:17.822Z</v>
+        <v>2026-08-06T00:00:02.866Z</v>
       </c>
       <c r="L13" t="str">
-        <v>2026-07-31T07:01:36.291Z</v>
+        <v>2026-08-06T00:55:47.704Z</v>
       </c>
       <c r="M13" t="str">
         <v/>
       </c>
-      <c r="N13" t="str">
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>APP_20260806_0013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>PAT_0d1e2f3a</v>
+      </c>
+      <c r="C14" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D14">
+        <v>8</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="F14" t="str">
+        <v>17:45</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Permanent Filling</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Checked In</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026-08-05T18:47:44.663Z</v>
+      </c>
+      <c r="J14" t="str">
+        <v>2026-08-06T00:00:06.284Z</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-08-06T00:00:06.284Z</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>APP_20260806_0014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>PAT_b8c9d0e1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="F15" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="G15" t="str">
+        <v>RPD Add Tooth</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Treatment Done</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2026-08-05T18:47:59.192Z</v>
+      </c>
+      <c r="J15" t="str">
+        <v>2026-08-05T19:36:58.831Z</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2026-08-05T18:58:09.055Z</v>
+      </c>
+      <c r="L15" t="str">
+        <v>2026-08-05T19:29:38.270Z</v>
+      </c>
+      <c r="M15" t="str">
+        <v>2026-08-05T19:36:58.831Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>APP_20260806_0015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>PAT_a7b8c9d0</v>
+      </c>
+      <c r="C16" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="F16" t="str">
+        <v>18:15</v>
+      </c>
+      <c r="G16" t="str">
+        <v>GIC Filling</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Checked In</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2026-08-05T18:48:13.447Z</v>
+      </c>
+      <c r="J16" t="str">
+        <v>2026-08-06T00:00:07.273Z</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-08-06T00:00:07.273Z</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>APP_20260806_0016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>PAT_b605a8bf</v>
+      </c>
+      <c r="C17" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="D17">
+        <v>11</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="F17" t="str">
+        <v>18:30</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Permanent Filling</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Checked In</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026-08-05T19:18:06.190Z</v>
+      </c>
+      <c r="J17" t="str">
+        <v>2026-08-05T19:20:16.852Z</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2026-08-05T19:20:16.852Z</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2009,10 +2675,57 @@
         <v>installment_number</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>PAY_b38c9c0a</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PAT_6f7a8b9c</v>
+      </c>
+      <c r="C2" t="str">
+        <v>TRT_d92703f7</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>500</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Cash</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2026-08-05</v>
+      </c>
+      <c r="K2" t="str">
+        <v>REC-1785951738124</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Paid</v>
+      </c>
+      <c r="M2" t="str">
+        <v>2026-08-05T17:42:18.257Z</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-08-05T17:42:18.258Z</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2152,6 +2865,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:K2"/>
   </ignoredErrors>
@@ -2222,7 +2936,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2270,13 +2984,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>TRT_bfb0fba7</v>
+        <v>TRT_415d5e6b</v>
       </c>
       <c r="B2" t="str">
-        <v>PAT_1a2b3c4d</v>
+        <v>PAT_5e6f7a8b</v>
       </c>
       <c r="C2" t="str">
-        <v>APP_20260728_0001</v>
+        <v>APP_20260805_0003</v>
       </c>
       <c r="D2" t="str">
         <v>DEN_0001</v>
@@ -2291,36 +3005,36 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>s</v>
+        <v/>
       </c>
       <c r="I2">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>1. Amoxicillin 250mg | Dose: BD | Duration: 1 day</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="M2" t="str">
-        <v>2026-07-28T12:34:40.740Z</v>
+        <v>2026-08-05T18:01:35.514Z</v>
       </c>
       <c r="N2" t="str">
-        <v>2026-07-28T12:34:40.740Z</v>
+        <v>2026-08-05T18:01:35.514Z</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TRT_47a0519c</v>
+        <v>TRT_2e02dd6e</v>
       </c>
       <c r="B3" t="str">
-        <v>PAT_3c4d5e6f</v>
+        <v>PAT_9c0d1e2f</v>
       </c>
       <c r="C3" t="str">
-        <v>APP_20260728_0002</v>
+        <v>APP_20260805_0005</v>
       </c>
       <c r="D3" t="str">
         <v>DEN_0001</v>
@@ -2335,36 +3049,36 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>123123</v>
+        <v/>
       </c>
       <c r="I3">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>1. Clindamycin | Dose: BD | Duration: 1 day</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="M3" t="str">
-        <v>2026-07-28T12:36:16.940Z</v>
+        <v>2026-08-05T18:02:46.525Z</v>
       </c>
       <c r="N3" t="str">
-        <v>2026-07-28T12:36:16.940Z</v>
+        <v>2026-08-05T18:02:46.525Z</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TRT_daf9d12d</v>
+        <v>TRT_96872335</v>
       </c>
       <c r="B4" t="str">
-        <v>PAT_a1b2c3d4</v>
+        <v>PAT_b4c5d6e7</v>
       </c>
       <c r="C4" t="str">
-        <v>APP_20260728_0006</v>
+        <v>APP_20260805_0004</v>
       </c>
       <c r="D4" t="str">
         <v>DEN_0001</v>
@@ -2379,36 +3093,36 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>u</v>
+        <v/>
       </c>
       <c r="I4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>2026-08-08</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-05</v>
       </c>
       <c r="M4" t="str">
-        <v>2026-07-28T12:37:12.919Z</v>
+        <v>2026-08-05T18:08:31.111Z</v>
       </c>
       <c r="N4" t="str">
-        <v>2026-07-28T12:37:12.919Z</v>
+        <v>2026-08-05T18:08:31.111Z</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TRT_e5a4363f</v>
+        <v>TRT_4769bf6e</v>
       </c>
       <c r="B5" t="str">
-        <v>PAT_7a8b9c0d</v>
+        <v>PAT_1a2b3c4d</v>
       </c>
       <c r="C5" t="str">
-        <v>APP_20260728_0004</v>
+        <v>APP_20260806_0006</v>
       </c>
       <c r="D5" t="str">
         <v>DEN_0001</v>
@@ -2423,31 +3137,211 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>;</v>
+        <v/>
       </c>
       <c r="I5">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>1. Diclofenac Sodium | Dose: bd | Duration: 1 day</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>2026-07-28</v>
+        <v>2026-08-06</v>
       </c>
       <c r="M5" t="str">
-        <v>2026-07-28T12:38:21.452Z</v>
+        <v>2026-08-05T19:24:42.014Z</v>
       </c>
       <c r="N5" t="str">
-        <v>2026-07-28T12:38:21.452Z</v>
+        <v>2026-08-05T19:24:42.014Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TRT_001e56c3</v>
+      </c>
+      <c r="B6" t="str">
+        <v>PAT_b8c9d0e1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>APP_20260806_0014</v>
+      </c>
+      <c r="D6" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>s</v>
+      </c>
+      <c r="I6">
+        <v>3000</v>
+      </c>
+      <c r="J6" t="str">
+        <v>1. Phenoxymethylpenicillin | Dose: bd | Duration: 1 day</v>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="M6" t="str">
+        <v>2026-08-05T19:36:58.788Z</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-08-05T19:36:58.788Z</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>TRT_a5a04f09</v>
+      </c>
+      <c r="B7" t="str">
+        <v>PAT_5e6f7a8b</v>
+      </c>
+      <c r="C7" t="str">
+        <v>APP_20260806_0009</v>
+      </c>
+      <c r="D7" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>h</v>
+      </c>
+      <c r="I7">
+        <v>5000</v>
+      </c>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Clindamycin | Dose: eod | Duration: 1 day
+2. Phenoxymethylpenicillin | Dose: tds | Duration: 1 day
+3. Diclofenac Sodium | Dose: bd | Duration: 1 day</v>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="M7" t="str">
+        <v>2026-08-05T19:46:37.072Z</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-08-05T19:46:37.072Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TRT_55dc3a9e</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PAT_3c4d5e6f</v>
+      </c>
+      <c r="C8" t="str">
+        <v>APP_20260806_0007</v>
+      </c>
+      <c r="D8" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="M8" t="str">
+        <v>2026-08-06T00:04:56.275Z</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-08-06T00:04:56.275Z</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>TRT_b41a15a5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PAT_8b9c0d1e</v>
+      </c>
+      <c r="C9" t="str">
+        <v>APP_20260806_0010</v>
+      </c>
+      <c r="D9" t="str">
+        <v>DEN_0001</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>5000</v>
+      </c>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Amoxicillin 250mg | Dose: bd | 1 day
+2. Azithromycin | Dose: qds | 2 days
+3. Metronidazole | Dose: sos | 4 days
+4. Nystatin | Dose: tds | 1 day</v>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>2026-08-06</v>
+      </c>
+      <c r="M9" t="str">
+        <v>2026-08-06T00:51:48.965Z</v>
+      </c>
+      <c r="N9" t="str">
+        <v>2026-08-06T00:51:48.965Z</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/dental_clinic_database.xlsx
+++ b/data/dental_clinic_database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TC\Documents\GitHub\ivory-backend\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2057114-5F08-4F60-A5C4-30D13C0A947E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E9018C-7639-41DC-9D6C-F8EA1EBAD498}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Patients" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="248">
   <si>
     <t>id</t>
   </si>
@@ -189,18 +189,12 @@
     <t>treatment_completed_at</t>
   </si>
   <si>
-    <t>APP_20260805_0001</t>
-  </si>
-  <si>
     <t>2026-08-05</t>
   </si>
   <si>
     <t>GIC Filling</t>
   </si>
   <si>
-    <t>APP_20260805_0002</t>
-  </si>
-  <si>
     <t>Temporary Filling</t>
   </si>
   <si>
@@ -234,9 +228,6 @@
     <t>Drugs</t>
   </si>
   <si>
-    <t>APP_20260806_0008</t>
-  </si>
-  <si>
     <t>APP_20260806_0009</t>
   </si>
   <si>
@@ -247,9 +238,6 @@
   </si>
   <si>
     <t>APP_20260806_0014</t>
-  </si>
-  <si>
-    <t>APP_20260806_0016</t>
   </si>
   <si>
     <t>treatment_id</t>
@@ -744,30 +732,6 @@
   </si>
   <si>
     <t>end_time</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:02:31.846Z</t>
-  </si>
-  <si>
-    <t>2026-08-05 23:34:17</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:03:12.097Z</t>
-  </si>
-  <si>
-    <t>2026-08-05 23:34:19</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:20:20.653Z</t>
-  </si>
-  <si>
-    <t>2026-08-06 00:59:38</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:20:22.347Z</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:20:24.304Z</t>
   </si>
   <si>
     <t>distance_km</t>
@@ -1257,138 +1221,138 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B14" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B16" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1409,71 +1373,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1491,12 +1400,12 @@
         <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
@@ -1507,7 +1416,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -1518,7 +1427,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
@@ -1529,7 +1438,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -1540,7 +1449,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
@@ -1551,7 +1460,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -1562,7 +1471,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -1573,7 +1482,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -1584,7 +1493,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1595,7 +1504,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1606,7 +1515,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1617,7 +1526,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -1628,7 +1537,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
@@ -1639,7 +1548,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
@@ -1650,7 +1559,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1787,31 +1696,31 @@
         <v>42</v>
       </c>
       <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>74</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>75</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>76</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>77</v>
-      </c>
-      <c r="H1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K1" t="s">
-        <v>81</v>
       </c>
       <c r="L1" t="s">
         <v>48</v>
@@ -1823,18 +1732,18 @@
         <v>11</v>
       </c>
       <c r="O1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D2">
         <v>500</v>
@@ -1852,22 +1761,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N2" t="s">
         <v>85</v>
-      </c>
-      <c r="J2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" t="s">
-        <v>86</v>
-      </c>
-      <c r="L2" t="s">
-        <v>87</v>
-      </c>
-      <c r="M2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N2" t="s">
-        <v>89</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -1888,7 +1797,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1896,42 +1805,42 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1958,13 +1867,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
         <v>48</v>
@@ -1976,10 +1885,10 @@
         <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K1" t="s">
         <v>2</v>
@@ -1987,66 +1896,66 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" t="s">
         <v>106</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" t="s">
         <v>108</v>
       </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>109</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>110</v>
       </c>
-      <c r="G2" t="s">
+      <c r="K2" t="s">
         <v>111</v>
-      </c>
-      <c r="H2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J2" t="s">
-        <v>114</v>
-      </c>
-      <c r="K2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" t="s">
         <v>116</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J3" t="s">
-        <v>120</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
@@ -2070,13 +1979,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E1" t="s">
         <v>42</v>
@@ -2085,7 +1994,7 @@
         <v>43</v>
       </c>
       <c r="G1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
@@ -2094,19 +2003,19 @@
         <v>47</v>
       </c>
       <c r="J1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K1" t="s">
         <v>48</v>
       </c>
       <c r="L1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="N1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="O1" t="s">
         <v>10</v>
@@ -2136,34 +2045,34 @@
         <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D1" t="s">
         <v>43</v>
       </c>
       <c r="E1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" t="s">
         <v>129</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>130</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>131</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>132</v>
-      </c>
-      <c r="I1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J1" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" t="s">
-        <v>135</v>
-      </c>
-      <c r="L1" t="s">
-        <v>136</v>
       </c>
       <c r="M1" t="s">
         <v>10</v>
@@ -2174,13 +2083,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
         <v>37</v>
@@ -2201,30 +2110,30 @@
         <v>3000</v>
       </c>
       <c r="J2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K2" t="s">
         <v>13</v>
       </c>
       <c r="L2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
         <v>37</v>
@@ -2245,30 +2154,30 @@
         <v>3000</v>
       </c>
       <c r="J3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="K3" t="s">
         <v>13</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
         <v>37</v>
@@ -2292,27 +2201,27 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>37</v>
@@ -2333,30 +2242,30 @@
         <v>6000</v>
       </c>
       <c r="J5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K5" t="s">
         <v>13</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>
@@ -2371,36 +2280,36 @@
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I6">
         <v>3000</v>
       </c>
       <c r="J6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K6" t="s">
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>37</v>
@@ -2415,36 +2324,36 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I7">
         <v>5000</v>
       </c>
       <c r="J7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K7" t="s">
         <v>13</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
@@ -2459,7 +2368,7 @@
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I8">
         <v>500</v>
@@ -2471,24 +2380,24 @@
         <v>13</v>
       </c>
       <c r="L8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -2503,25 +2412,25 @@
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I9">
         <v>5000</v>
       </c>
       <c r="J9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K9" t="s">
         <v>13</v>
       </c>
       <c r="L9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="N9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2542,10 +2451,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D1" t="s">
         <v>10</v>
@@ -2556,342 +2465,342 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C2">
         <v>20000</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C3">
         <v>75000</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4">
         <v>5000</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C5">
         <v>3000</v>
       </c>
       <c r="D5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C6">
         <v>20000</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>2000</v>
       </c>
       <c r="D7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C8">
         <v>30000</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C9">
         <v>150000</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>5000</v>
       </c>
       <c r="D10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>6000</v>
       </c>
       <c r="D11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C12">
         <v>5000</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C13">
         <v>5000</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14">
         <v>3000</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C15">
         <v>15000</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>5000</v>
       </c>
       <c r="D16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C17">
         <v>30000</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C18">
         <v>60000</v>
       </c>
       <c r="D18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C19">
         <v>40000</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E19" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C20">
         <v>80000</v>
       </c>
       <c r="D20" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E20" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C21">
         <v>500</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/data/dental_clinic_database.xlsx
+++ b/data/dental_clinic_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TC\Documents\GitHub\ivory-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D042A620-3703-45A7-9DA4-1EFB2261FD92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E05487-5066-4407-AB2F-00DA6B4724FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-72" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dentists" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="476">
   <si>
     <t>id</t>
   </si>
@@ -963,33 +963,6 @@
     <t>installment_number</t>
   </si>
   <si>
-    <t>PAY_b38c9c0a</t>
-  </si>
-  <si>
-    <t>PAT_6f7a8b9c</t>
-  </si>
-  <si>
-    <t>TRT_d92703f7</t>
-  </si>
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>REC-1785951738124</t>
-  </si>
-  <si>
-    <t>Paid</t>
-  </si>
-  <si>
-    <t>2026-08-05T17:42:18.257Z</t>
-  </si>
-  <si>
-    <t>2026-08-05T17:42:18.258Z</t>
-  </si>
-  <si>
     <t>Dental Clinic Simple Test Excel</t>
   </si>
   <si>
@@ -1146,122 +1119,6 @@
     <t>treatment_date</t>
   </si>
   <si>
-    <t>TRT_415d5e6b</t>
-  </si>
-  <si>
-    <t>PAT_5e6f7a8b</t>
-  </si>
-  <si>
-    <t>APP_20260805_0003</t>
-  </si>
-  <si>
-    <t>1. Amoxicillin 250mg | Dose: BD | Duration: 1 day</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:01:35.514Z</t>
-  </si>
-  <si>
-    <t>TRT_2e02dd6e</t>
-  </si>
-  <si>
-    <t>PAT_9c0d1e2f</t>
-  </si>
-  <si>
-    <t>APP_20260805_0005</t>
-  </si>
-  <si>
-    <t>1. Clindamycin | Dose: BD | Duration: 1 day</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:02:46.525Z</t>
-  </si>
-  <si>
-    <t>TRT_96872335</t>
-  </si>
-  <si>
-    <t>PAT_b4c5d6e7</t>
-  </si>
-  <si>
-    <t>APP_20260805_0004</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:08:31.111Z</t>
-  </si>
-  <si>
-    <t>TRT_4769bf6e</t>
-  </si>
-  <si>
-    <t>PAT_1a2b3c4d</t>
-  </si>
-  <si>
-    <t>1. Diclofenac Sodium | Dose: bd | Duration: 1 day</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:24:42.014Z</t>
-  </si>
-  <si>
-    <t>TRT_001e56c3</t>
-  </si>
-  <si>
-    <t>PAT_b8c9d0e1</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>1. Phenoxymethylpenicillin | Dose: bd | Duration: 1 day</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:36:58.788Z</t>
-  </si>
-  <si>
-    <t>TRT_a5a04f09</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>1. Clindamycin | Dose: eod | Duration: 1 day_x000D__x000D_
-2. Phenoxymethylpenicillin | Dose: tds | Duration: 1 day_x000D__x000D_
-3. Diclofenac Sodium | Dose: bd | Duration: 1 day</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:46:37.072Z</t>
-  </si>
-  <si>
-    <t>TRT_55dc3a9e</t>
-  </si>
-  <si>
-    <t>PAT_3c4d5e6f</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>2026-08-06T00:04:56.275Z</t>
-  </si>
-  <si>
-    <t>TRT_b41a15a5</t>
-  </si>
-  <si>
-    <t>PAT_8b9c0d1e</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1. Amoxicillin 250mg | Dose: bd | 1 day_x000D__x000D_
-2. Azithromycin | Dose: qds | 2 days_x000D__x000D_
-3. Metronidazole | Dose: sos | 4 days_x000D__x000D_
-4. Nystatin | Dose: tds | 1 day</t>
-  </si>
-  <si>
-    <t>2026-08-06T00:51:48.965Z</t>
-  </si>
-  <si>
     <t>treatment_name</t>
   </si>
   <si>
@@ -1500,36 +1357,6 @@
   </si>
   <si>
     <t>end_time</t>
-  </si>
-  <si>
-    <t>APP_20260805_0001</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:02:31.846Z</t>
-  </si>
-  <si>
-    <t>2026-08-05 23:34:17</t>
-  </si>
-  <si>
-    <t>APP_20260805_0002</t>
-  </si>
-  <si>
-    <t>2026-08-05T18:03:12.097Z</t>
-  </si>
-  <si>
-    <t>2026-08-05 23:34:19</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:20:20.653Z</t>
-  </si>
-  <si>
-    <t>2026-08-06 00:59:38</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:20:22.347Z</t>
-  </si>
-  <si>
-    <t>2026-08-05T19:20:24.304Z</t>
   </si>
   <si>
     <t>distance_km</t>
@@ -2010,9 +1837,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2032,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2063,9 +1890,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2073,140 +1900,140 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="B2" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>454</v>
+        <v>408</v>
       </c>
       <c r="B3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="B4" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>458</v>
+        <v>412</v>
       </c>
       <c r="B5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>460</v>
+        <v>414</v>
       </c>
       <c r="B6" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>462</v>
+        <v>416</v>
       </c>
       <c r="B7" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="B8" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>466</v>
+        <v>420</v>
       </c>
       <c r="B9" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>468</v>
+        <v>422</v>
       </c>
       <c r="B10" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="B11" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>472</v>
+        <v>426</v>
       </c>
       <c r="B12" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>474</v>
+        <v>428</v>
       </c>
       <c r="B13" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="B14" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="B15" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>480</v>
+        <v>434</v>
       </c>
       <c r="B16" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>482</v>
+        <v>436</v>
       </c>
       <c r="B17" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="B18" t="s">
-        <v>485</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -2219,79 +2046,24 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>486</v>
+        <v>440</v>
       </c>
       <c r="C1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B2" t="s">
-        <v>489</v>
-      </c>
-      <c r="C2" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>491</v>
-      </c>
-      <c r="B3" t="s">
-        <v>492</v>
-      </c>
-      <c r="C3" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" t="s">
-        <v>494</v>
-      </c>
-      <c r="C4" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B6" t="s">
-        <v>497</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C6" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2299,9 +2071,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2309,12 +2081,12 @@
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>499</v>
+        <v>443</v>
       </c>
       <c r="B2" t="s">
         <v>31</v>
@@ -2323,9 +2095,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>500</v>
+        <v>444</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -2334,42 +2106,42 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>501</v>
+        <v>445</v>
       </c>
       <c r="B4" t="s">
-        <v>502</v>
+        <v>446</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>447</v>
       </c>
       <c r="B5" t="s">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="C5">
         <v>10.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>505</v>
+        <v>449</v>
       </c>
       <c r="B6" t="s">
-        <v>506</v>
+        <v>450</v>
       </c>
       <c r="C6">
         <v>11.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>507</v>
+        <v>451</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -2378,31 +2150,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>508</v>
+        <v>452</v>
       </c>
       <c r="B8" t="s">
-        <v>509</v>
+        <v>453</v>
       </c>
       <c r="C8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>510</v>
+        <v>454</v>
       </c>
       <c r="B9" t="s">
-        <v>511</v>
+        <v>455</v>
       </c>
       <c r="C9">
         <v>3.3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>512</v>
+        <v>456</v>
       </c>
       <c r="B10" t="s">
         <v>56</v>
@@ -2411,9 +2183,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>513</v>
+        <v>457</v>
       </c>
       <c r="B11" t="s">
         <v>87</v>
@@ -2422,20 +2194,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>514</v>
+        <v>458</v>
       </c>
       <c r="B12" t="s">
-        <v>515</v>
+        <v>459</v>
       </c>
       <c r="C12">
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>516</v>
+        <v>460</v>
       </c>
       <c r="B13" t="s">
         <v>144</v>
@@ -2444,31 +2216,31 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>517</v>
+        <v>461</v>
       </c>
       <c r="B14" t="s">
-        <v>518</v>
+        <v>462</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>519</v>
+        <v>463</v>
       </c>
       <c r="B15" t="s">
-        <v>520</v>
+        <v>464</v>
       </c>
       <c r="C15">
         <v>7.7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>521</v>
+        <v>465</v>
       </c>
       <c r="B16" t="s">
         <v>139</v>
@@ -2477,9 +2249,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>522</v>
+        <v>466</v>
       </c>
       <c r="B17" t="s">
         <v>120</v>
@@ -2488,9 +2260,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>523</v>
+        <v>467</v>
       </c>
       <c r="B18" t="s">
         <v>126</v>
@@ -2499,9 +2271,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>524</v>
+        <v>468</v>
       </c>
       <c r="B19" t="s">
         <v>46</v>
@@ -2510,9 +2282,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>525</v>
+        <v>469</v>
       </c>
       <c r="B20" t="s">
         <v>161</v>
@@ -2521,34 +2293,34 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>526</v>
+        <v>470</v>
       </c>
       <c r="B21" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="C21">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>528</v>
+        <v>472</v>
       </c>
       <c r="B22" t="s">
-        <v>529</v>
+        <v>473</v>
       </c>
       <c r="C22">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>530</v>
+        <v>474</v>
       </c>
       <c r="B23" t="s">
-        <v>531</v>
+        <v>475</v>
       </c>
       <c r="C23">
         <v>20</v>
@@ -2565,9 +2337,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2605,7 +2377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2643,7 +2415,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -2681,7 +2453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2719,7 +2491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2757,7 +2529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2795,7 +2567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -2833,7 +2605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2871,7 +2643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -2909,7 +2681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2947,7 +2719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -2985,7 +2757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -3023,7 +2795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -3061,7 +2833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -3099,7 +2871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -3137,7 +2909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -3175,7 +2947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -3213,7 +2985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -3251,7 +3023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -3289,7 +3061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -3327,7 +3099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -3365,7 +3137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -3403,7 +3175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>88</v>
       </c>
@@ -3441,7 +3213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -3479,7 +3251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -3517,7 +3289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -3555,7 +3327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -3593,7 +3365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -3631,7 +3403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -3669,7 +3441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>109</v>
       </c>
@@ -3707,7 +3479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -3745,7 +3517,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>117</v>
       </c>
@@ -3783,7 +3555,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>123</v>
       </c>
@@ -3821,7 +3593,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>129</v>
       </c>
@@ -3859,7 +3631,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>132</v>
       </c>
@@ -3897,7 +3669,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>136</v>
       </c>
@@ -3935,7 +3707,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>141</v>
       </c>
@@ -3973,7 +3745,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>146</v>
       </c>
@@ -4011,7 +3783,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -4049,7 +3821,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>154</v>
       </c>
@@ -4087,7 +3859,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -4125,7 +3897,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>163</v>
       </c>
@@ -4163,7 +3935,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -4201,7 +3973,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>171</v>
       </c>
@@ -4239,7 +4011,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>175</v>
       </c>
@@ -4277,7 +4049,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>179</v>
       </c>
@@ -4315,7 +4087,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>183</v>
       </c>
@@ -4353,7 +4125,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -4402,9 +4174,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4439,7 +4211,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -4474,7 +4246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>205</v>
       </c>
@@ -4509,7 +4281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>210</v>
       </c>
@@ -4544,7 +4316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>213</v>
       </c>
@@ -4579,7 +4351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>216</v>
       </c>
@@ -4614,7 +4386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>220</v>
       </c>
@@ -4649,7 +4421,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>223</v>
       </c>
@@ -4684,7 +4456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>226</v>
       </c>
@@ -4719,7 +4491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>229</v>
       </c>
@@ -4754,7 +4526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>232</v>
       </c>
@@ -4789,7 +4561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>235</v>
       </c>
@@ -4824,7 +4596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>238</v>
       </c>
@@ -4859,7 +4631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>241</v>
       </c>
@@ -4894,7 +4666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>245</v>
       </c>
@@ -4929,7 +4701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>248</v>
       </c>
@@ -4964,7 +4736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>251</v>
       </c>
@@ -4999,7 +4771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>255</v>
       </c>
@@ -5034,7 +4806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>258</v>
       </c>
@@ -5069,7 +4841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>261</v>
       </c>
@@ -5104,7 +4876,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>264</v>
       </c>
@@ -5139,7 +4911,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>267</v>
       </c>
@@ -5174,7 +4946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -5209,7 +4981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>273</v>
       </c>
@@ -5244,7 +5016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>276</v>
       </c>
@@ -5279,7 +5051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>279</v>
       </c>
@@ -5314,7 +5086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>282</v>
       </c>
@@ -5349,7 +5121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>285</v>
       </c>
@@ -5384,7 +5156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>288</v>
       </c>
@@ -5419,7 +5191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>291</v>
       </c>
@@ -5454,7 +5226,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>294</v>
       </c>
@@ -5489,7 +5261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>297</v>
       </c>
@@ -5531,10 +5303,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5579,59 +5351,12 @@
       </c>
       <c r="O1" t="s">
         <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D2">
-        <v>500</v>
-      </c>
-      <c r="E2">
-        <v>500</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>500</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>313</v>
-      </c>
-      <c r="J2" t="s">
-        <v>314</v>
-      </c>
-      <c r="K2" t="s">
-        <v>315</v>
-      </c>
-      <c r="L2" t="s">
-        <v>316</v>
-      </c>
-      <c r="M2" t="s">
-        <v>317</v>
-      </c>
-      <c r="N2" t="s">
-        <v>318</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:O2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:O1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5639,54 +5364,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B7" t="s">
         <v>320</v>
-      </c>
-      <c r="B3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>328</v>
-      </c>
-      <c r="B7" t="s">
-        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -5703,9 +5428,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5713,13 +5438,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D1" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="F1" t="s">
         <v>197</v>
@@ -5731,109 +5456,109 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="J1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="K1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I2" t="s">
+        <v>333</v>
+      </c>
+      <c r="J2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K2" t="s">
         <v>335</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>336</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>337</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>329</v>
+      </c>
+      <c r="F3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G3" t="s">
         <v>338</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H3" t="s">
+        <v>338</v>
+      </c>
+      <c r="I3" t="s">
         <v>339</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J3" t="s">
         <v>340</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>341</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" t="s">
         <v>342</v>
       </c>
-      <c r="J2" t="s">
+      <c r="E4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G4" t="s">
         <v>343</v>
       </c>
-      <c r="K2" t="s">
+      <c r="H4" t="s">
+        <v>343</v>
+      </c>
+      <c r="I4" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="J4" t="s">
         <v>345</v>
-      </c>
-      <c r="B3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C3" t="s">
-        <v>346</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>338</v>
-      </c>
-      <c r="F3" t="s">
-        <v>339</v>
-      </c>
-      <c r="G3" t="s">
-        <v>347</v>
-      </c>
-      <c r="H3" t="s">
-        <v>347</v>
-      </c>
-      <c r="I3" t="s">
-        <v>348</v>
-      </c>
-      <c r="J3" t="s">
-        <v>349</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>350</v>
-      </c>
-      <c r="B4" t="s">
-        <v>346</v>
-      </c>
-      <c r="C4" t="s">
-        <v>351</v>
-      </c>
-      <c r="E4" t="s">
-        <v>338</v>
-      </c>
-      <c r="G4" t="s">
-        <v>352</v>
-      </c>
-      <c r="H4" t="s">
-        <v>352</v>
-      </c>
-      <c r="I4" t="s">
-        <v>353</v>
-      </c>
-      <c r="J4" t="s">
-        <v>354</v>
       </c>
       <c r="K4" t="s">
         <v>21</v>
@@ -5850,20 +5575,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C1" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E1" t="s">
         <v>191</v>
@@ -5872,7 +5597,7 @@
         <v>192</v>
       </c>
       <c r="G1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="H1" t="s">
         <v>2</v>
@@ -5881,19 +5606,19 @@
         <v>196</v>
       </c>
       <c r="J1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="K1" t="s">
         <v>197</v>
       </c>
       <c r="L1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="M1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="N1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="O1" t="s">
         <v>4</v>
@@ -5912,10 +5637,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5923,398 +5648,46 @@
         <v>191</v>
       </c>
       <c r="C1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D1" t="s">
         <v>192</v>
       </c>
       <c r="E1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="H1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="I1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="J1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="K1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="L1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M1" t="s">
         <v>4</v>
       </c>
       <c r="N1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2">
-        <v>3000</v>
-      </c>
-      <c r="J2" t="s">
-        <v>374</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s">
-        <v>314</v>
-      </c>
-      <c r="M2" t="s">
-        <v>375</v>
-      </c>
-      <c r="N2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3">
-        <v>3000</v>
-      </c>
-      <c r="J3" t="s">
-        <v>379</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s">
-        <v>314</v>
-      </c>
-      <c r="M3" t="s">
-        <v>380</v>
-      </c>
-      <c r="N3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>381</v>
-      </c>
-      <c r="B4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4">
-        <v>5000</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>384</v>
-      </c>
-      <c r="L4" t="s">
-        <v>314</v>
-      </c>
-      <c r="M4" t="s">
-        <v>385</v>
-      </c>
-      <c r="N4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>386</v>
-      </c>
-      <c r="B5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5">
-        <v>6000</v>
-      </c>
-      <c r="J5" t="s">
-        <v>388</v>
-      </c>
-      <c r="K5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M5" t="s">
-        <v>389</v>
-      </c>
-      <c r="N5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>390</v>
-      </c>
-      <c r="B6" t="s">
-        <v>391</v>
-      </c>
-      <c r="C6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I6">
-        <v>3000</v>
-      </c>
-      <c r="J6" t="s">
-        <v>393</v>
-      </c>
-      <c r="K6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" t="s">
-        <v>200</v>
-      </c>
-      <c r="M6" t="s">
-        <v>394</v>
-      </c>
-      <c r="N6" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>395</v>
-      </c>
-      <c r="B7" t="s">
-        <v>372</v>
-      </c>
-      <c r="C7" t="s">
-        <v>229</v>
-      </c>
-      <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>396</v>
-      </c>
-      <c r="I7">
-        <v>5000</v>
-      </c>
-      <c r="J7" t="s">
-        <v>397</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" t="s">
-        <v>200</v>
-      </c>
-      <c r="M7" t="s">
-        <v>398</v>
-      </c>
-      <c r="N7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>399</v>
-      </c>
-      <c r="B8" t="s">
-        <v>400</v>
-      </c>
-      <c r="C8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" t="s">
-        <v>401</v>
-      </c>
-      <c r="I8">
-        <v>500</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" t="s">
-        <v>200</v>
-      </c>
-      <c r="M8" t="s">
-        <v>402</v>
-      </c>
-      <c r="N8" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>403</v>
-      </c>
-      <c r="B9" t="s">
-        <v>404</v>
-      </c>
-      <c r="C9" t="s">
-        <v>232</v>
-      </c>
-      <c r="D9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" t="s">
-        <v>405</v>
-      </c>
-      <c r="I9">
-        <v>5000</v>
-      </c>
-      <c r="J9" t="s">
-        <v>406</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" t="s">
-        <v>200</v>
-      </c>
-      <c r="M9" t="s">
-        <v>407</v>
-      </c>
-      <c r="N9" t="s">
-        <v>407</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6322,17 +5695,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>408</v>
+        <v>362</v>
       </c>
       <c r="C1" t="s">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -6341,9 +5714,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>410</v>
+        <v>364</v>
       </c>
       <c r="B2" t="s">
         <v>218</v>
@@ -6352,32 +5725,32 @@
         <v>20000</v>
       </c>
       <c r="D2" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="B3" t="s">
-        <v>413</v>
+        <v>367</v>
       </c>
       <c r="C3">
         <v>75000</v>
       </c>
       <c r="D3" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>414</v>
+        <v>368</v>
       </c>
       <c r="B4" t="s">
         <v>253</v>
@@ -6386,117 +5759,117 @@
         <v>5000</v>
       </c>
       <c r="D4" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="B5" t="s">
-        <v>416</v>
+        <v>370</v>
       </c>
       <c r="C5">
         <v>3000</v>
       </c>
       <c r="D5" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>417</v>
+        <v>371</v>
       </c>
       <c r="B6" t="s">
-        <v>418</v>
+        <v>372</v>
       </c>
       <c r="C6">
         <v>20000</v>
       </c>
       <c r="D6" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>419</v>
+        <v>373</v>
       </c>
       <c r="B7" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="C7">
         <v>2000</v>
       </c>
       <c r="D7" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E7" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="B8" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="C8">
         <v>30000</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>378</v>
       </c>
       <c r="C9">
         <v>150000</v>
       </c>
       <c r="D9" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E9" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="B10" t="s">
-        <v>426</v>
+        <v>380</v>
       </c>
       <c r="C10">
         <v>5000</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E10" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>427</v>
+        <v>381</v>
       </c>
       <c r="B11" t="s">
         <v>243</v>
@@ -6505,185 +5878,185 @@
         <v>6000</v>
       </c>
       <c r="D11" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E11" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>428</v>
+        <v>382</v>
       </c>
       <c r="B12" t="s">
-        <v>429</v>
+        <v>383</v>
       </c>
       <c r="C12">
         <v>5000</v>
       </c>
       <c r="D12" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E12" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>430</v>
+        <v>384</v>
       </c>
       <c r="B13" t="s">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="C13">
         <v>5000</v>
       </c>
       <c r="D13" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E13" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>432</v>
+        <v>386</v>
       </c>
       <c r="B14" t="s">
-        <v>433</v>
+        <v>387</v>
       </c>
       <c r="C14">
         <v>3000</v>
       </c>
       <c r="D14" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E14" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>434</v>
+        <v>388</v>
       </c>
       <c r="B15" t="s">
-        <v>435</v>
+        <v>389</v>
       </c>
       <c r="C15">
         <v>15000</v>
       </c>
       <c r="D15" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E15" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>436</v>
+        <v>390</v>
       </c>
       <c r="B16" t="s">
-        <v>437</v>
+        <v>391</v>
       </c>
       <c r="C16">
         <v>5000</v>
       </c>
       <c r="D16" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E16" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>438</v>
+        <v>392</v>
       </c>
       <c r="B17" t="s">
-        <v>439</v>
+        <v>393</v>
       </c>
       <c r="C17">
         <v>30000</v>
       </c>
       <c r="D17" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E17" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>440</v>
+        <v>394</v>
       </c>
       <c r="B18" t="s">
-        <v>441</v>
+        <v>395</v>
       </c>
       <c r="C18">
         <v>60000</v>
       </c>
       <c r="D18" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>442</v>
+        <v>396</v>
       </c>
       <c r="B19" t="s">
-        <v>443</v>
+        <v>397</v>
       </c>
       <c r="C19">
         <v>40000</v>
       </c>
       <c r="D19" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E19" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>444</v>
+        <v>398</v>
       </c>
       <c r="B20" t="s">
-        <v>445</v>
+        <v>399</v>
       </c>
       <c r="C20">
         <v>80000</v>
       </c>
       <c r="D20" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E20" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>446</v>
+        <v>400</v>
       </c>
       <c r="B21" t="s">
-        <v>447</v>
+        <v>401</v>
       </c>
       <c r="C21">
         <v>500</v>
       </c>
       <c r="D21" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="E21" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="B22" t="s">
         <v>202</v>
@@ -6692,15 +6065,15 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>449</v>
+        <v>403</v>
       </c>
       <c r="E22" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>450</v>
+        <v>404</v>
       </c>
       <c r="B23" t="s">
         <v>207</v>
@@ -6709,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
       <c r="E23" t="s">
-        <v>451</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/data/dental_clinic_database.xlsx
+++ b/data/dental_clinic_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TC\Documents\GitHub\ivory-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E05487-5066-4407-AB2F-00DA6B4724FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A097227-2FF9-43AD-A40A-704A1C18C655}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dentists" sheetId="1" r:id="rId1"/>
@@ -1837,9 +1837,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1890,9 +1890,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>406</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>408</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>410</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>412</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>414</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>416</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>418</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>420</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>422</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>424</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>426</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>428</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>430</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>432</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>434</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>436</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>438</v>
       </c>
@@ -2047,9 +2047,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2071,9 +2071,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>443</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>444</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>445</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>447</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>449</v>
       </c>
@@ -2139,7 +2139,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>451</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>452</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>454</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>456</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>457</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>458</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>460</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>461</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>463</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>465</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>466</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>467</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>468</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>469</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>470</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>472</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>474</v>
       </c>
@@ -2337,9 +2337,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L48"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>88</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>97</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>106</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>109</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>117</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>123</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>129</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>132</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>136</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>141</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>146</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>154</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>163</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>171</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>175</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>179</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>183</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>187</v>
       </c>
@@ -4174,9 +4174,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K32"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>199</v>
       </c>
@@ -4246,7 +4246,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>205</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>210</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>213</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>216</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>220</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>223</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>226</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>229</v>
       </c>
@@ -4526,7 +4526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>232</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>235</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>238</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>241</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>245</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>248</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>251</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>255</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>258</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>261</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>264</v>
       </c>
@@ -4911,7 +4911,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>267</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>270</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>273</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>276</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>279</v>
       </c>
@@ -5086,7 +5086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>282</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>285</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>288</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>291</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>294</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>297</v>
       </c>
@@ -5304,9 +5304,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5364,9 +5364,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>310</v>
       </c>
@@ -5374,7 +5374,7 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>311</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>313</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>315</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>317</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>319</v>
       </c>
@@ -5428,9 +5428,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>326</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>336</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>341</v>
       </c>
@@ -5575,9 +5575,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5638,9 +5638,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5695,9 +5695,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>364</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>366</v>
       </c>
@@ -5748,7 +5748,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>368</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>369</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>371</v>
       </c>
@@ -5799,7 +5799,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>373</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>375</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>377</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>379</v>
       </c>
@@ -5867,7 +5867,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>381</v>
       </c>
@@ -5884,7 +5884,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>382</v>
       </c>
@@ -5901,7 +5901,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>384</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>386</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>388</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>390</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>392</v>
       </c>
@@ -5986,7 +5986,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>394</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>396</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>398</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>400</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>402</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>404</v>
       </c>
